--- a/data/ISA6_EN_6.0.3.xlsx
+++ b/data/ISA6_EN_6.0.3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://reuttergroup365.sharepoint.com/sites/REUTIB-ITTopicsandBCM2025/Freigegebene Dokumente/Chat/02 PM/05 TISAX_ENX Certification &amp; Applicatbility/02 Material/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enxa-my.sharepoint.com/personal/pierre-alexis_delaunay_enx_com/Documents/Documents/Projects/TISAX/ISA6_TRANSLATION/EN/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{76636E65-AB14-404E-8DBA-7AB1A45FB58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE0D7C82-1AFC-9548-AE1B-0FD45A056D5E}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="16980" tabRatio="755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="16980" tabRatio="755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Welcome" sheetId="88" r:id="rId1"/>
@@ -125,13 +125,6 @@
     <definedName name="Control9.4">#REF!</definedName>
     <definedName name="Control9.5">#REF!</definedName>
     <definedName name="Control9.6">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Cover!$B$1:$C$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Data Protection'!$A$1:$W$25</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">Definitions!$B$1:$E$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Examples KPI'!$A$1:$AQ$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Maturity levels'!$B$1:$H$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">Results!$A$1:$H$103</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Welcome!$B$1:$B$8</definedName>
     <definedName name="er" localSheetId="10">#REF!</definedName>
     <definedName name="er" localSheetId="3">#REF!</definedName>
     <definedName name="er" localSheetId="2">#REF!</definedName>
@@ -868,6 +861,13 @@
     <definedName name="VDA_9_6" localSheetId="2">#REF!</definedName>
     <definedName name="VDA_9_6" localSheetId="5">'Prototype Protection'!#REF!</definedName>
     <definedName name="VDA_9_6">#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Cover!$B$1:$C$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Data Protection'!$A$1:$W$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">Definitions!$B$1:$E$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Examples KPI'!$A$1:$AQ$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Maturity levels'!$B$1:$H$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">Results!$A$1:$H$103</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Welcome!$B$1:$B$8</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -7365,9 +7365,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="89">
     <font>
@@ -9481,11 +9481,11 @@
     <xf numFmtId="0" fontId="11" fillId="25" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -9530,7 +9530,7 @@
     <xf numFmtId="0" fontId="13" fillId="22" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -9596,7 +9596,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="465" applyFont="1" applyFill="1"/>
@@ -9621,7 +9621,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -9655,7 +9655,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -9672,7 +9672,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -9708,7 +9708,7 @@
     <xf numFmtId="0" fontId="34" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -9869,7 +9869,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="465" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="465" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -9922,7 +9922,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="36" fillId="0" borderId="0" xfId="465" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="0" xfId="465" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -9947,7 +9947,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="465" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="465" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -9968,7 +9968,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="27" xfId="465" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="27" xfId="465" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -9996,7 +9996,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="10" xfId="465" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="10" xfId="465" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -10010,7 +10010,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="465" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="465" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="465" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="465" applyFont="1" applyAlignment="1">
@@ -10027,7 +10027,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -10351,7 +10351,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="60" xfId="465" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="60" xfId="465" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -10678,19 +10678,19 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="465" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="79" fillId="28" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="28" borderId="44" xfId="518" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="28" borderId="47" xfId="518" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="28" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="28" borderId="52" xfId="518" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10702,28 +10702,22 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="28" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="77" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="70" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="28" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="85" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -10735,7 +10729,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -10822,238 +10822,6 @@
     <cellStyle name="Berechnung 2 3 3" xfId="624" xr:uid="{248F40EB-A5C5-4B82-87E9-77387A24872D}"/>
     <cellStyle name="Berechnung 2 4" xfId="573" xr:uid="{F7118CBF-F961-4F59-90B6-F6EBC93DBE50}"/>
     <cellStyle name="Berechnung 2 5" xfId="572" xr:uid="{1D3004BF-8717-4BCC-8F04-F6C1FE1EDF1F}"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="206" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="326" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="310" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="282" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="254" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="234" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="418" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="416" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="352" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="280" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="312" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="332" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="364" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="396" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="420" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="452" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="446" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="426" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="26" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="46" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="28" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="8" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="6" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="16" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="14" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="414" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="428" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="344" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="320" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="354" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="298" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="222" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="190" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="322" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="328" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="296" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="276" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="336" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="432" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="434" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="370" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="238" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="266" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="286" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="250" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="316" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="424" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="404" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="380" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="360" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="454" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="456" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="442" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="430" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="410" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="422" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="444" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="462" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="348" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="372" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="392" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="412" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="436" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="400" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="294" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="278" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="258" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="338" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="402" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="464" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="368" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="304" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="284" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="308" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="340" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="210" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="170" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="274" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="262" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="448" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="300" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="388" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="458" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="40" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="20" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="4" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="18" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="50" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="32" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="406" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="438" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="460" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="440" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="408" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="376" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="356" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="324" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="292" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="288" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="384" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="450" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="386" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="246" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="270" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="290" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="318" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="198" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="214" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="156" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="108" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="140" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="86" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="196" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="164" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="64" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="236" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="244" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="252" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="268" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="212" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="228" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="70" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="172" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="188" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="204" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="60" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="92" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="124" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="150" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="138" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="122" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="102" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="90" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="74" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="10" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="42" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="116" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="94" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="168" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="232" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="382" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="394" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="378" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="350" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="334" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="272" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="224" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="208" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="184" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="66" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="82" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="98" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="126" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="142" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="152" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="100" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="68" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="34" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="44" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="302" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="314" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="242" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="202" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="218" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="182" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="178" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="174" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="194" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="186" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="230" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="166" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="226" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="306" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="48" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="148" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="110" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="56" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="248" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="366" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="342" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="136" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="54" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="112" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="160" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="128" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="58" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="260" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="220" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="180" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="76" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="256" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="330" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="358" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="374" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="390" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="398" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="362" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="264" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="200" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="114" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="158" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="24" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="12" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="22" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="36" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="80" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="106" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="118" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="134" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="144" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="154" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="96" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="72" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="346" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="120" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="104" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="88" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="78" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="62" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="176" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="192" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="216" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="240" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="132" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="162" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="146" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="130" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="84" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="38" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="30" builtinId="9" hidden="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="52" builtinId="9" hidden="1"/>
     <cellStyle name="Check Cell" xfId="528" xr:uid="{00000000-0005-0000-0000-00001F010000}"/>
     <cellStyle name="Eingabe 2" xfId="513" xr:uid="{00000000-0005-0000-0000-000020010000}"/>
     <cellStyle name="Eingabe 2 2" xfId="534" xr:uid="{00000000-0005-0000-0000-000021010000}"/>
@@ -11101,241 +10869,474 @@
     <cellStyle name="Komma 2" xfId="538" xr:uid="{00000000-0005-0000-0000-000033010000}"/>
     <cellStyle name="Komma 2 2" xfId="542" xr:uid="{00000000-0005-0000-0000-000034010000}"/>
     <cellStyle name="Komma 2 2 2" xfId="587" xr:uid="{651A5F1C-E858-430E-8A9F-1325EDC1686F}"/>
-    <cellStyle name="Link" xfId="347" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="357" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="363" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="329" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="265" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="267" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="275" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="281" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="289" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="291" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="245" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="251" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="257" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="237" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="233" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="229" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="243" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="283" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="273" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="361" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="349" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="339" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="305" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="293" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="435" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="239" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="271" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="343" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="415" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="455" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="453" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="429" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="405" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="395" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="61" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="65" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="69" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="77" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="81" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="73" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="311" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="325" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="253" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="269" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="353" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="321" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="375" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="367" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="351" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="327" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="319" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="303" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="279" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="263" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="255" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="101" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="231" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="359" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="457" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="413" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="393" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="297" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="299" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="301" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="309" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="99" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="437" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="445" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="449" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="451" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="461" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="463" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="447" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="407" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="399" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="431" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="417" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="421" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="425" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="433" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="401" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="403" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="397" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="389" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="409" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="427" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="411" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="439" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="459" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="441" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="307" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="371" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="423" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="247" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="287" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="335" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="391" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="249" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="419" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="71" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="57" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="443" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="383" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="295" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="315" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="261" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="241" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="235" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="285" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="277" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="259" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="355" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="199" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="203" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="211" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="219" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="221" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="227" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="207" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="175" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="159" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="45" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="49" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="55" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="217" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="137" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="145" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="147" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="155" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="157" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="163" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="171" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="173" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="167" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="121" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="129" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="135" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="109" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="113" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="107" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="103" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="117" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="119" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="165" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="153" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="139" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="53" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="143" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="223" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="201" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="189" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="177" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="15" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="123" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="379" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="365" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="179" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="225" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="59" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="47" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="9" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="5" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="43" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="79" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="89" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="313" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="317" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="323" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="331" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="333" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="341" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="345" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="337" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="33" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="141" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="213" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="131" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="125" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="149" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="111" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="209" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="191" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="215" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="205" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="187" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="169" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="161" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="151" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="133" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="115" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="105" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="369" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="373" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="377" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="387" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="381" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="197" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="67" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="19" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="27" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="87" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="63" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="181" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="183" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="185" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="193" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="195" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="385" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="17" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="21" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="7" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="3" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="1" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="11" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="37" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="29" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="93" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="85" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="51" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="127" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="75" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="25" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="31" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="35" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="39" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="41" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="13" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="95" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="97" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="23" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="91" builtinId="8" hidden="1"/>
-    <cellStyle name="Link" xfId="83" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="347" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="357" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="363" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="329" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="265" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="267" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="275" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="281" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="289" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="291" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="245" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="251" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="257" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="237" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="233" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="229" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="243" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="283" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="273" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="361" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="349" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="339" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="305" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="293" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="435" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="239" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="271" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="343" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="415" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="455" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="453" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="429" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="405" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="395" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="61" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="65" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="69" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="77" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="81" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="73" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="311" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="325" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="253" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="269" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="353" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="321" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="375" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="367" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="351" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="327" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="319" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="303" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="279" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="263" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="255" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="101" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="231" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="359" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="457" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="413" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="393" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="297" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="299" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="301" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="309" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="99" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="437" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="445" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="449" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="451" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="461" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="463" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="447" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="407" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="399" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="431" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="417" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="421" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="425" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="433" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="401" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="403" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="397" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="389" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="409" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="427" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="411" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="439" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="459" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="441" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="307" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="371" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="423" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="247" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="287" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="335" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="391" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="249" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="419" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="71" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="57" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="443" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="383" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="295" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="315" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="261" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="241" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="235" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="285" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="277" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="259" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="355" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="199" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="203" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="211" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="219" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="221" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="227" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="207" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="175" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="159" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="45" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="49" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="55" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="217" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="137" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="145" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="147" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="155" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="157" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="163" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="171" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="173" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="167" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="121" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="129" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="135" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="109" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="113" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="107" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="103" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="117" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="119" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="165" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="153" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="139" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="53" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="143" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="223" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="201" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="189" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="177" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="15" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="123" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="379" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="365" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="179" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="225" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="59" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="47" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="9" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="5" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="43" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="79" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="89" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="313" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="317" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="323" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="331" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="333" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="341" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="345" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="337" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="33" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="141" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="213" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="131" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="125" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="149" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="111" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="209" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="191" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="215" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="205" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="187" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="169" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="161" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="151" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="133" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="115" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="105" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="369" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="373" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="377" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="387" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="381" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="197" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="67" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="19" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="27" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="87" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="63" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="181" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="183" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="185" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="193" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="195" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="385" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="17" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="21" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="7" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="3" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="11" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="37" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="29" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="93" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="85" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="51" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="127" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="75" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="25" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="31" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="35" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="39" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="41" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="13" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="95" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="97" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="23" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="91" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte" xfId="83" builtinId="8" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="206" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="326" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="310" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="282" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="254" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="234" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="418" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="416" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="352" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="280" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="312" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="332" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="364" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="396" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="420" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="452" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="446" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="426" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="26" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="46" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="28" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="8" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="6" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="16" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="14" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="414" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="428" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="344" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="320" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="354" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="298" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="222" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="190" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="322" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="328" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="296" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="276" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="336" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="432" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="434" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="370" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="238" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="266" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="286" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="250" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="316" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="424" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="404" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="380" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="360" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="454" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="456" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="442" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="430" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="410" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="422" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="444" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="462" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="348" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="372" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="392" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="412" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="436" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="400" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="294" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="278" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="258" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="338" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="402" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="464" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="368" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="304" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="284" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="308" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="340" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="210" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="170" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="274" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="262" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="448" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="300" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="388" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="458" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="40" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="20" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="4" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="18" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="50" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="32" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="406" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="438" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="460" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="440" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="408" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="376" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="356" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="324" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="292" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="288" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="384" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="450" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="386" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="246" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="270" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="290" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="318" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="198" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="214" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="156" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="108" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="140" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="86" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="196" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="164" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="64" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="236" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="244" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="252" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="268" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="212" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="228" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="70" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="172" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="188" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="204" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="60" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="92" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="124" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="150" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="138" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="122" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="102" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="90" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="74" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="10" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="42" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="116" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="94" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="168" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="232" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="382" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="394" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="378" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="350" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="334" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="272" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="224" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="208" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="184" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="66" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="82" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="98" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="126" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="142" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="152" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="100" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="68" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="34" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="44" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="302" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="314" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="242" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="202" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="218" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="182" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="178" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="174" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="194" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="186" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="230" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="166" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="226" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="306" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="48" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="148" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="110" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="56" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="248" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="366" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="342" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="136" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="54" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="112" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="160" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="128" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="58" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="260" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="220" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="180" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="76" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="256" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="330" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="358" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="374" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="390" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="398" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="362" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="264" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="200" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="114" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="158" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="24" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="12" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="22" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="36" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="80" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="106" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="118" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="134" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="144" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="154" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="96" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="72" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="346" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="120" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="104" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="88" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="78" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="62" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="176" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="192" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="216" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="240" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="132" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="162" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="146" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="130" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="84" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="38" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="30" builtinId="9" hidden="1"/>
+    <cellStyle name="Lien hypertexte visité" xfId="52" builtinId="9" hidden="1"/>
     <cellStyle name="Link 2" xfId="529" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
     <cellStyle name="Linked Cell" xfId="526" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
     <cellStyle name="Neutral 2" xfId="514" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="539" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
     <cellStyle name="Normal 3" xfId="531" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
     <cellStyle name="Normal 3 2" xfId="541" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
@@ -11360,7 +11361,6 @@
     <cellStyle name="Note 3 3" xfId="623" xr:uid="{E59416D4-8593-405D-9D8A-1FCB56688C1F}"/>
     <cellStyle name="Note 4" xfId="576" xr:uid="{BB6DB719-42BC-4D28-AD59-B69E18DA1B1E}"/>
     <cellStyle name="Note 5" xfId="569" xr:uid="{6C35D08E-1032-49ED-B817-75DD2002D521}"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="465" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
     <cellStyle name="Standard 3" xfId="643" xr:uid="{8D6B6EEB-7A51-489F-813E-52B6E3F8D3BB}"/>
     <cellStyle name="Standard 5" xfId="540" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
@@ -11388,7 +11388,7 @@
     <cellStyle name="Überschrift 5" xfId="525" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
     <cellStyle name="Warnender Text 2" xfId="527" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
   </cellStyles>
-  <dxfs count="323">
+  <dxfs count="324">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -11398,6 +11398,31 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="52"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -11414,7 +11439,32 @@
         <i val="0"/>
         <condense val="0"/>
         <extend val="0"/>
+        <color indexed="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <color indexed="52"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color indexed="57"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color theme="1"/>
       </font>
     </dxf>
     <dxf>
@@ -11448,24 +11498,13 @@
       <font>
         <b/>
         <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <b/>
         <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <color indexed="57"/>
       </font>
     </dxf>
@@ -11473,8 +11512,6 @@
       <font>
         <b/>
         <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <color indexed="52"/>
       </font>
     </dxf>
@@ -11482,16 +11519,21 @@
       <font>
         <b/>
         <i val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
+        <color indexed="57"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
         <color indexed="10"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
-        <color theme="1"/>
+        <color indexed="52"/>
       </font>
     </dxf>
     <dxf>
@@ -11514,82 +11556,6 @@
         <i val="0"/>
         <color indexed="10"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color indexed="57"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color indexed="52"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color indexed="57"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color indexed="52"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <fill>
@@ -11675,6 +11641,25 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.24994659260841701"/>
@@ -11709,9 +11694,58 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -11764,25 +11798,6 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="1"/>
       </font>
     </dxf>
@@ -11794,21 +11809,6 @@
         <patternFill>
           <fgColor theme="0"/>
           <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
       <border>
@@ -11837,8 +11837,108 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -11866,6 +11966,29 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.24994659260841701"/>
@@ -11882,13 +12005,36 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
+        <color auto="1"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <color theme="1"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -11946,10 +12092,11 @@
       <font>
         <b/>
         <i val="0"/>
+        <color theme="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11967,22 +12114,67 @@
       <font>
         <b/>
         <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
       </font>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -12020,123 +12212,15 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
+        <b/>
+        <i val="0"/>
       </font>
-      <fill>
-        <patternFill>
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <font>
         <b/>
         <i val="0"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -12206,58 +12290,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
       <border>
@@ -12270,9 +12305,13 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
       <border>
@@ -12297,6 +12336,12 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
       </font>
       <fill>
@@ -12309,46 +12354,6 @@
       <font>
         <b/>
         <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
         <color theme="1"/>
       </font>
       <fill>
@@ -12356,21 +12361,6 @@
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -12417,6 +12407,21 @@
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -12815,6 +12820,11 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.24994659260841701"/>
@@ -12860,17 +12870,6 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="0"/>
       </font>
       <fill>
@@ -12907,6 +12906,45 @@
       <font>
         <b/>
         <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
         <color theme="1"/>
       </font>
       <fill>
@@ -12935,7 +12973,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -12968,7 +13006,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -12981,39 +13019,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -13066,6 +13071,40 @@
         <b/>
         <i val="0"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -13172,26 +13211,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
+          <bgColor rgb="FFBFBFBF"/>
         </patternFill>
       </fill>
       <border>
@@ -13225,7 +13245,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFBFBFBF"/>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
       <border>
@@ -13241,6 +13261,25 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
       <border>
@@ -13491,21 +13530,6 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <color theme="0"/>
       </font>
@@ -13525,13 +13549,9 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
       <fill>
         <patternFill>
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
       <border>
@@ -13748,9 +13768,13 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
       <border>
@@ -13763,13 +13787,9 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
       <fill>
         <patternFill>
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
       <border>
@@ -13884,9 +13904,18 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
       <border>
@@ -13925,32 +13954,61 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
         <color theme="1"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -13976,59 +14034,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -14069,10 +14074,11 @@
       <font>
         <b/>
         <i val="0"/>
+        <color theme="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -14092,11 +14098,10 @@
       <font>
         <b/>
         <i val="0"/>
-        <color theme="1"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -14493,7 +14498,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
+      <numFmt numFmtId="166" formatCode="[$-409]dd\-mmm\-yy;@"/>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -15299,7 +15304,7 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
+      <numFmt numFmtId="166" formatCode="[$-409]dd\-mmm\-yy;@"/>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -16084,7 +16089,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
+      <numFmt numFmtId="166" formatCode="[$-409]dd\-mmm\-yy;@"/>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
@@ -17201,7 +17206,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -17650,7 +17655,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -18847,164 +18852,164 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle68" displayName="Tabelle68" ref="B2:H23" totalsRowShown="0" headerRowDxfId="322" dataDxfId="321">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabelle68" displayName="Tabelle68" ref="B2:H23" totalsRowShown="0" headerRowDxfId="323" dataDxfId="322">
   <autoFilter ref="B2:H23" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name=" " dataDxfId="320"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Maturity level 0" dataDxfId="319"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Maturity level 1" dataDxfId="318"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Maturity level 2" dataDxfId="317"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Maturity level 3" dataDxfId="316"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Maturity level 4" dataDxfId="315"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Maturity level 5" dataDxfId="314"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name=" " dataDxfId="321"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Maturity level 0" dataDxfId="320"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Maturity level 1" dataDxfId="319"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Maturity level 2" dataDxfId="318"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Maturity level 3" dataDxfId="317"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Maturity level 4" dataDxfId="316"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Maturity level 5" dataDxfId="315"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabelle6" displayName="Tabelle6" ref="B27:E57" totalsRowShown="0" headerRowDxfId="313" dataDxfId="312">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabelle6" displayName="Tabelle6" ref="B27:E57" totalsRowShown="0" headerRowDxfId="314" dataDxfId="313">
   <autoFilter ref="B27:E57" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B28:E57">
     <sortCondition ref="B27:B57"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Term" dataDxfId="311"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name=" " dataDxfId="310"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Explanation" dataDxfId="309"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Examples" dataDxfId="308"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Term" dataDxfId="312"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name=" " dataDxfId="311"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Explanation" dataDxfId="310"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Examples" dataDxfId="309"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabelle9" displayName="Tabelle9" ref="B16:E24" totalsRowShown="0" headerRowDxfId="307" dataDxfId="306">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabelle9" displayName="Tabelle9" ref="B16:E24" totalsRowShown="0" headerRowDxfId="308" dataDxfId="307">
   <autoFilter ref="B16:E24" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Term" dataDxfId="305"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name=" " dataDxfId="304"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Explanation" dataDxfId="303"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Examples" dataDxfId="302"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Term" dataDxfId="306"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name=" " dataDxfId="305"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Explanation" dataDxfId="304"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Examples" dataDxfId="303"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="ISMS_Checkliste" displayName="ISMS_Checkliste" ref="A2:AB66" totalsRowShown="0" headerRowDxfId="301" dataDxfId="300">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="ISMS_Checkliste" displayName="ISMS_Checkliste" ref="A2:AB66" totalsRowShown="0" headerRowDxfId="302" dataDxfId="301">
   <autoFilter ref="A2:AB66" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB66">
     <sortCondition ref="C2:C66"/>
   </sortState>
   <tableColumns count="28">
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Row_Format" dataDxfId="299">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Row_Format" dataDxfId="300">
       <calculatedColumnFormula>IF(AND($B3&lt;&gt;"",$C$3="1",NOT(ISBLANK($C3))),"header",IF(AND($B3&lt;&gt;"",$C$3&lt;&gt;"1",NOT(ISBLANK($C3))),"blank",IF(AND($B3&lt;&gt;"",#REF!="01",NOT(ISBLANK(#REF!))),"header",IF(AND($B3&lt;&gt;"",#REF!&lt;&gt;"01",NOT(ISBLANK(#REF!))),"blank",IF(AND($B3&lt;&gt;"",#REF!&lt;&gt;"01",NOT(ISBLANK(#REF!))),"blank",IF(AND($C$3="1",ISBLANK($C3),ISBLANK($B3)),"blank","control"))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Is_Title?" dataDxfId="298"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Control number" dataDxfId="297"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Maturity level" dataDxfId="296"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0300-00001C000000}" name="Implementation description" dataDxfId="295"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Reference documentation" dataDxfId="294"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Findings/Assessment result" dataDxfId="293"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="Control question" dataDxfId="292"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="Objective" dataDxfId="291"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0300-00001E000000}" name="Requirements_x000a_(must)" dataDxfId="290"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Requirements_x000a_(should)" dataDxfId="289"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0300-00001F000000}" name="Additional requirements_x000a_for high protection needs" dataDxfId="288"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0300-000020000000}" name="Additional requirements_x000a_for very high protection needs" dataDxfId="287"/>
-    <tableColumn id="4" xr3:uid="{CADD8F51-F82D-4665-B276-CD6A0754390A}" name="Additional requirements for Simplified Group Assessments (SGA)" dataDxfId="286"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="Usual person responsible for process implementation" dataDxfId="285"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Reference to other standards" dataDxfId="284"/>
-    <tableColumn id="29" xr3:uid="{EBB5DC99-932B-498C-BDC9-1CA616E8F436}" name="Reference to implementation guidance" dataDxfId="283"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="Measures/recommendations" dataDxfId="282"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="Date of assessment" dataDxfId="281"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="Date of completion" dataDxfId="280"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="Responsible department" dataDxfId="279"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="Contact" dataDxfId="278"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Further information" dataDxfId="277"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0300-000016000000}" name="Support:_x000a_Examples “Normal protection need”" dataDxfId="276"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0300-000017000000}" name="Support:_x000a_Examples “High protection need”" dataDxfId="275"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0300-000019000000}" name="Support:_x000a_Examples “Very high protection need”" dataDxfId="274"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0300-00001A000000}" name="Possible questions (examples, not mandatory)" dataDxfId="273"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0300-00001B000000}" name="Possible evidence (not mandatory)" dataDxfId="272"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Is_Title?" dataDxfId="299"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Control number" dataDxfId="298"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Maturity level" dataDxfId="297"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0300-00001C000000}" name="Implementation description" dataDxfId="296"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Reference documentation" dataDxfId="295"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Findings/Assessment result" dataDxfId="294"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="Control question" dataDxfId="293"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0300-00000E000000}" name="Objective" dataDxfId="292"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0300-00001E000000}" name="Requirements_x000a_(must)" dataDxfId="291"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Requirements_x000a_(should)" dataDxfId="290"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0300-00001F000000}" name="Additional requirements_x000a_for high protection needs" dataDxfId="289"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0300-000020000000}" name="Additional requirements_x000a_for very high protection needs" dataDxfId="288"/>
+    <tableColumn id="4" xr3:uid="{CADD8F51-F82D-4665-B276-CD6A0754390A}" name="Additional requirements for Simplified Group Assessments (SGA)" dataDxfId="287"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0300-00000D000000}" name="Usual person responsible for process implementation" dataDxfId="286"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Reference to other standards" dataDxfId="285"/>
+    <tableColumn id="29" xr3:uid="{EBB5DC99-932B-498C-BDC9-1CA616E8F436}" name="Reference to implementation guidance" dataDxfId="284"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0300-000010000000}" name="Measures/recommendations" dataDxfId="283"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0300-000011000000}" name="Date of assessment" dataDxfId="282"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0300-000012000000}" name="Date of completion" dataDxfId="281"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0300-000013000000}" name="Responsible department" dataDxfId="280"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0300-000014000000}" name="Contact" dataDxfId="279"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0300-000015000000}" name="Further information" dataDxfId="278"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0300-000016000000}" name="Support:_x000a_Examples “Normal protection need”" dataDxfId="277"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0300-000017000000}" name="Support:_x000a_Examples “High protection need”" dataDxfId="276"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0300-000019000000}" name="Support:_x000a_Examples “Very high protection need”" dataDxfId="275"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0300-00001A000000}" name="Possible questions (examples, not mandatory)" dataDxfId="274"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0300-00001B000000}" name="Possible evidence (not mandatory)" dataDxfId="273"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="ISMS_Checkliste4" displayName="ISMS_Checkliste4" ref="A2:Z30" totalsRowShown="0" headerRowDxfId="271" dataDxfId="270">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="ISMS_Checkliste4" displayName="ISMS_Checkliste4" ref="A2:Z30" totalsRowShown="0" headerRowDxfId="272" dataDxfId="271">
   <autoFilter ref="A2:Z30" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:Z30">
     <sortCondition ref="C2:C30"/>
   </sortState>
   <tableColumns count="26">
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Row_Format" dataDxfId="269">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Row_Format" dataDxfId="270">
       <calculatedColumnFormula>IF(AND($B3="x",$C$3="1",NOT(ISBLANK($C3))),"header",IF(AND($B3="x",$C$3&lt;&gt;"1",NOT(ISBLANK($C3))),"blank",IF(AND($B3="x",#REF!="01",NOT(ISBLANK(#REF!))),"header",IF(AND($B3="x",#REF!&lt;&gt;"01",NOT(ISBLANK(#REF!))),"blank",IF(AND($B3="x",#REF!&lt;&gt;"01",NOT(ISBLANK(#REF!))),"blank",IF(AND($C$3="1",ISBLANK($C3),ISBLANK($B3)),"blank","control"))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Is_Title?" dataDxfId="268"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Control number" dataDxfId="267"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Maturity level" dataDxfId="266"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0400-00001C000000}" name="Implementation description" dataDxfId="265"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Reference documentation" dataDxfId="264"/>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Findings/Assessment result" dataDxfId="263"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="Control question" dataDxfId="262"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" name="Objective" dataDxfId="261"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0400-00001E000000}" name="Requirements_x000a_(must)" dataDxfId="260"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="Requirements_x000a_(should)" dataDxfId="259"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0400-00001F000000}" name="Additional requirements_x000a_for vehicles classified as requiring protection" dataDxfId="258"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" name="Usual person responsible for process implementation " dataDxfId="257"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Reference to other standards" dataDxfId="256"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" name="Measures/recommendations" dataDxfId="255"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0400-000011000000}" name="Date of assessment" dataDxfId="254"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" name="Date of completion" dataDxfId="253"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" name="Responsible department" dataDxfId="252"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" name="Contact" dataDxfId="251"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0400-000015000000}" name="Further information" dataDxfId="250"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0400-000016000000}" name="Support:_x000a_Examples “Normal protection need”" dataDxfId="249"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0400-000017000000}" name="Support:_x000a_Examples “High protection need”" dataDxfId="248"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0400-000018000000}" name="Support:_x000a_Examples “Very high protection need”" dataDxfId="247"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" name="Possible questions (examples, not mandatory)" dataDxfId="246"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0400-00001A000000}" name="Possible evidence (not mandatory)" dataDxfId="245"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0400-00001B000000}" name="Column4" dataDxfId="244"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Is_Title?" dataDxfId="269"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Control number" dataDxfId="268"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="Maturity level" dataDxfId="267"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0400-00001C000000}" name="Implementation description" dataDxfId="266"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Reference documentation" dataDxfId="265"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Findings/Assessment result" dataDxfId="264"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="Control question" dataDxfId="263"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0400-00000E000000}" name="Objective" dataDxfId="262"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0400-00001E000000}" name="Requirements_x000a_(must)" dataDxfId="261"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0400-00000B000000}" name="Requirements_x000a_(should)" dataDxfId="260"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0400-00001F000000}" name="Additional requirements_x000a_for vehicles classified as requiring protection" dataDxfId="259"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0400-00000D000000}" name="Usual person responsible for process implementation " dataDxfId="258"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Reference to other standards" dataDxfId="257"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0400-000010000000}" name="Measures/recommendations" dataDxfId="256"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0400-000011000000}" name="Date of assessment" dataDxfId="255"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0400-000012000000}" name="Date of completion" dataDxfId="254"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0400-000013000000}" name="Responsible department" dataDxfId="253"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0400-000014000000}" name="Contact" dataDxfId="252"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0400-000015000000}" name="Further information" dataDxfId="251"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0400-000016000000}" name="Support:_x000a_Examples “Normal protection need”" dataDxfId="250"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0400-000017000000}" name="Support:_x000a_Examples “High protection need”" dataDxfId="249"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0400-000018000000}" name="Support:_x000a_Examples “Very high protection need”" dataDxfId="248"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0400-000019000000}" name="Possible questions (examples, not mandatory)" dataDxfId="247"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0400-00001A000000}" name="Possible evidence (not mandatory)" dataDxfId="246"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0400-00001B000000}" name="Column4" dataDxfId="245"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{E4582D05-640A-4260-8035-AF46FDEA7304}" name="ISMS_Checkliste3" displayName="ISMS_Checkliste3" ref="A4:W26" totalsRowShown="0" headerRowDxfId="243" dataDxfId="242">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{E4582D05-640A-4260-8035-AF46FDEA7304}" name="ISMS_Checkliste3" displayName="ISMS_Checkliste3" ref="A4:W26" totalsRowShown="0" headerRowDxfId="244" dataDxfId="243">
   <autoFilter ref="A4:W26" xr:uid="{A3E29917-96FD-4DA0-86AF-6D4C40A78D4B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:W25">
     <sortCondition ref="C4:C25"/>
   </sortState>
   <tableColumns count="23">
-    <tableColumn id="5" xr3:uid="{4E6B94F6-5A37-499F-AB81-EB975701BDDB}" name="Row_Format" dataDxfId="241">
+    <tableColumn id="5" xr3:uid="{4E6B94F6-5A37-499F-AB81-EB975701BDDB}" name="Row_Format" dataDxfId="242">
       <calculatedColumnFormula>IF(AND($B5&lt;&gt;"",$C$5="1",NOT(ISBLANK($C5))),"header",IF(AND($B5&lt;&gt;"",$C$5&lt;&gt;"1",NOT(ISBLANK($C5))),"broke",IF(AND($B5&lt;&gt;"",#REF!="01",NOT(ISBLANK(#REF!))),"header",IF(AND($B5&lt;&gt;"",#REF!&lt;&gt;"01",NOT(ISBLANK(#REF!))),"broke",IF(AND($B5&lt;&gt;"",#REF!&lt;&gt;"01",NOT(ISBLANK(#REF!))),"broke",IF(AND($C$5="1",ISBLANK($C5),ISBLANK($B5)),"broke","Control"))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F8B98606-DA2C-4265-BB69-49772C814F78}" name="Is_Title?" dataDxfId="240"/>
-    <tableColumn id="9" xr3:uid="{FAACECCB-6AFD-4E8B-9AA4-A0973054F7AA}" name="Control number" dataDxfId="239"/>
-    <tableColumn id="8" xr3:uid="{9D9AE427-94E8-4F75-969C-9BD91FAFB091}" name="Assessment" dataDxfId="238"/>
-    <tableColumn id="28" xr3:uid="{C6FB4D25-F647-48AE-90BC-45FC4A2B7CB3}" name="Description of implementation" dataDxfId="237"/>
-    <tableColumn id="2" xr3:uid="{98BE86F1-4352-492C-A0A6-5F8304BAEC65}" name="Reference Documentation" dataDxfId="236"/>
-    <tableColumn id="1" xr3:uid="{3AD0F2FC-4503-4A3C-80BB-C7EADED0340C}" name="Findings/test result" dataDxfId="235"/>
-    <tableColumn id="10" xr3:uid="{86F51B85-6D24-463B-A2F2-BBCA29711584}" name="Control question" dataDxfId="234"/>
-    <tableColumn id="14" xr3:uid="{C24E1292-AAFC-4E39-A226-DFD3597CFDD1}" name="Objective" dataDxfId="233"/>
-    <tableColumn id="30" xr3:uid="{A622686B-91B0-45DC-98F3-CABB1B16354B}" name="Requirements _x000a_(must)" dataDxfId="232"/>
-    <tableColumn id="13" xr3:uid="{C534F0D5-DE93-4D2D-87B7-E2669ED96C80}" name="Usual person responsible for process implementation " dataDxfId="231"/>
-    <tableColumn id="3" xr3:uid="{593CF527-E2CE-46E8-9135-8FCA2A5B5032}" name="Reference to other standards" dataDxfId="230"/>
-    <tableColumn id="16" xr3:uid="{2D4EC799-91D6-4AAE-BF47-89AA02A39E5C}" name="Measures/recommendations" dataDxfId="229"/>
-    <tableColumn id="17" xr3:uid="{0F1F3899-034B-4E1E-9B13-0F31DA9F6E0A}" name="Date of assessment" dataDxfId="228"/>
-    <tableColumn id="18" xr3:uid="{46185C28-76E1-4317-A402-1F46CEDDD776}" name="Date of completion" dataDxfId="227"/>
-    <tableColumn id="19" xr3:uid="{403D7ADC-913B-4390-A247-A06EB45C3D79}" name="Responsible department" dataDxfId="226"/>
-    <tableColumn id="20" xr3:uid="{1648F56B-742C-4828-A304-ABE09A7ABEDA}" name="Contact" dataDxfId="225"/>
-    <tableColumn id="21" xr3:uid="{675421D1-7322-4903-8572-39A731C3F436}" name="Further information" dataDxfId="224"/>
-    <tableColumn id="22" xr3:uid="{787EC722-4C19-43CD-8615-60FC32BA628D}" name="Assistance:_x000a_Examples of &quot;normal protection needs&quot;" dataDxfId="223"/>
-    <tableColumn id="23" xr3:uid="{4D08930B-DB9F-4E7A-8110-169DCE8B628D}" name="Assistance:_x000a_Examples of &quot;High protection requirements&quot;" dataDxfId="222"/>
-    <tableColumn id="25" xr3:uid="{38DC258A-752D-41CE-93A2-9DFA08B1874A}" name="Assistance:_x000a_Examples of &quot;very high protection needs&quot;" dataDxfId="221"/>
-    <tableColumn id="26" xr3:uid="{FB734419-0A52-4951-A556-6FD764F76276}" name="Possible questions (examples, not binding)" dataDxfId="220"/>
-    <tableColumn id="27" xr3:uid="{46689C84-906B-4AFA-A849-EC5A671B958F}" name="Possible evidence (not binding)" dataDxfId="219"/>
+    <tableColumn id="6" xr3:uid="{F8B98606-DA2C-4265-BB69-49772C814F78}" name="Is_Title?" dataDxfId="241"/>
+    <tableColumn id="9" xr3:uid="{FAACECCB-6AFD-4E8B-9AA4-A0973054F7AA}" name="Control number" dataDxfId="240"/>
+    <tableColumn id="8" xr3:uid="{9D9AE427-94E8-4F75-969C-9BD91FAFB091}" name="Assessment" dataDxfId="239"/>
+    <tableColumn id="28" xr3:uid="{C6FB4D25-F647-48AE-90BC-45FC4A2B7CB3}" name="Description of implementation" dataDxfId="238"/>
+    <tableColumn id="2" xr3:uid="{98BE86F1-4352-492C-A0A6-5F8304BAEC65}" name="Reference Documentation" dataDxfId="237"/>
+    <tableColumn id="1" xr3:uid="{3AD0F2FC-4503-4A3C-80BB-C7EADED0340C}" name="Findings/test result" dataDxfId="236"/>
+    <tableColumn id="10" xr3:uid="{86F51B85-6D24-463B-A2F2-BBCA29711584}" name="Control question" dataDxfId="235"/>
+    <tableColumn id="14" xr3:uid="{C24E1292-AAFC-4E39-A226-DFD3597CFDD1}" name="Objective" dataDxfId="234"/>
+    <tableColumn id="30" xr3:uid="{A622686B-91B0-45DC-98F3-CABB1B16354B}" name="Requirements _x000a_(must)" dataDxfId="233"/>
+    <tableColumn id="13" xr3:uid="{C534F0D5-DE93-4D2D-87B7-E2669ED96C80}" name="Usual person responsible for process implementation " dataDxfId="232"/>
+    <tableColumn id="3" xr3:uid="{593CF527-E2CE-46E8-9135-8FCA2A5B5032}" name="Reference to other standards" dataDxfId="231"/>
+    <tableColumn id="16" xr3:uid="{2D4EC799-91D6-4AAE-BF47-89AA02A39E5C}" name="Measures/recommendations" dataDxfId="230"/>
+    <tableColumn id="17" xr3:uid="{0F1F3899-034B-4E1E-9B13-0F31DA9F6E0A}" name="Date of assessment" dataDxfId="229"/>
+    <tableColumn id="18" xr3:uid="{46185C28-76E1-4317-A402-1F46CEDDD776}" name="Date of completion" dataDxfId="228"/>
+    <tableColumn id="19" xr3:uid="{403D7ADC-913B-4390-A247-A06EB45C3D79}" name="Responsible department" dataDxfId="227"/>
+    <tableColumn id="20" xr3:uid="{1648F56B-742C-4828-A304-ABE09A7ABEDA}" name="Contact" dataDxfId="226"/>
+    <tableColumn id="21" xr3:uid="{675421D1-7322-4903-8572-39A731C3F436}" name="Further information" dataDxfId="225"/>
+    <tableColumn id="22" xr3:uid="{787EC722-4C19-43CD-8615-60FC32BA628D}" name="Assistance:_x000a_Examples of &quot;normal protection needs&quot;" dataDxfId="224"/>
+    <tableColumn id="23" xr3:uid="{4D08930B-DB9F-4E7A-8110-169DCE8B628D}" name="Assistance:_x000a_Examples of &quot;High protection requirements&quot;" dataDxfId="223"/>
+    <tableColumn id="25" xr3:uid="{38DC258A-752D-41CE-93A2-9DFA08B1874A}" name="Assistance:_x000a_Examples of &quot;very high protection needs&quot;" dataDxfId="222"/>
+    <tableColumn id="26" xr3:uid="{FB734419-0A52-4951-A556-6FD764F76276}" name="Possible questions (examples, not binding)" dataDxfId="221"/>
+    <tableColumn id="27" xr3:uid="{46689C84-906B-4AFA-A849-EC5A671B958F}" name="Possible evidence (not binding)" dataDxfId="220"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -29590,299 +29595,299 @@
     <mergeCell ref="C1:Y1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2:H34 A35:C35 A36:H66">
-    <cfRule type="expression" dxfId="218" priority="163">
+    <cfRule type="expression" dxfId="219" priority="163">
       <formula>$A2="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:R2 U2:AB2 A3:AB4 A5:M5 O5 R5:AB22 A6:O6 A7:M8 O7:O8 A9:O18 A19:M19 O19 A20:O22 K23:O23 A23:I24 R23:AS24 L24:O24 A25:O34 A35:C35 A36:O38 A39:J39 L39:O39 A40:O52 A53:J53 M53:O53 A54:O56 A57:L57 N57:O57 R57:V57 R58:AB59 A58:O66 S60:AB61 Q62:AB66">
-    <cfRule type="expression" dxfId="217" priority="152">
+    <cfRule type="expression" dxfId="218" priority="152">
       <formula>$A2="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C34 C36:C66">
-    <cfRule type="expression" dxfId="216" priority="568">
+    <cfRule type="expression" dxfId="217" priority="568">
       <formula>#REF!="01"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35">
-    <cfRule type="expression" dxfId="215" priority="122">
+    <cfRule type="expression" dxfId="216" priority="122">
       <formula>#REF!="01"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D34 D36:D66">
-    <cfRule type="cellIs" dxfId="214" priority="606" operator="between">
+    <cfRule type="cellIs" dxfId="215" priority="606" operator="between">
       <formula>0</formula>
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="213" priority="605" operator="between">
+    <cfRule type="cellIs" dxfId="214" priority="603" operator="between">
+      <formula>3</formula>
+      <formula>3.99999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="213" priority="604" operator="between">
+      <formula>4</formula>
+      <formula>5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="212" priority="605" operator="between">
       <formula>2</formula>
       <formula>2.99999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="212" priority="604" operator="between">
-      <formula>4</formula>
-      <formula>5</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="211" priority="603" operator="between">
-      <formula>3</formula>
-      <formula>3.99999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="210" priority="602" operator="equal">
+    <cfRule type="cellIs" dxfId="211" priority="602" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35">
-    <cfRule type="cellIs" dxfId="209" priority="111" operator="equal">
+    <cfRule type="cellIs" dxfId="210" priority="111" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="208" priority="108">
+    <cfRule type="expression" dxfId="209" priority="108">
       <formula>$A35="header"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="207" priority="115" operator="between">
-      <formula>0</formula>
-      <formula>2</formula>
+    <cfRule type="expression" dxfId="208" priority="109">
+      <formula>$A35="blank"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="206" priority="114" operator="between">
-      <formula>2</formula>
-      <formula>2.99999</formula>
+    <cfRule type="expression" dxfId="207" priority="110">
+      <formula>$A35="header"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="206" priority="112" operator="between">
+      <formula>3</formula>
+      <formula>3.99999</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="205" priority="113" operator="between">
       <formula>4</formula>
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="204" priority="112" operator="between">
-      <formula>3</formula>
-      <formula>3.99999</formula>
+    <cfRule type="cellIs" dxfId="204" priority="114" operator="between">
+      <formula>2</formula>
+      <formula>2.99999</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="203" priority="110">
-      <formula>$A35="header"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="202" priority="109">
-      <formula>$A35="blank"</formula>
+    <cfRule type="cellIs" dxfId="203" priority="115" operator="between">
+      <formula>0</formula>
+      <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35:H35">
-    <cfRule type="expression" dxfId="201" priority="120">
+    <cfRule type="expression" dxfId="202" priority="120">
       <formula>$A35="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:I34 H36:I66 I55:N55">
-    <cfRule type="expression" dxfId="200" priority="601">
+    <cfRule type="expression" dxfId="201" priority="601">
       <formula>#REF!="01"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H35:I35">
-    <cfRule type="expression" dxfId="199" priority="123">
+    <cfRule type="expression" dxfId="200" priority="123">
       <formula>#REF!="01"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J23:J24">
-    <cfRule type="expression" dxfId="198" priority="140">
-      <formula>$A23="blank"</formula>
+    <cfRule type="expression" dxfId="199" priority="139">
+      <formula>$A23="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="197" priority="141">
+    <cfRule type="expression" dxfId="198" priority="141">
       <formula>#REF!="01"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="196" priority="139">
-      <formula>$A23="header"</formula>
+    <cfRule type="expression" dxfId="197" priority="140">
+      <formula>$A23="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K24">
-    <cfRule type="expression" dxfId="195" priority="7">
+    <cfRule type="expression" dxfId="196" priority="7">
       <formula>#REF!="01"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="195" priority="6">
+      <formula>$A24="blank"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="194" priority="5">
       <formula>$A24="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="193" priority="6">
-      <formula>$A24="blank"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K53">
+    <cfRule type="expression" dxfId="193" priority="9">
+      <formula>$A53="blank"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="192" priority="8">
       <formula>$A53="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="191" priority="9">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L53">
+    <cfRule type="expression" dxfId="191" priority="13">
       <formula>$A53="blank"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L53">
     <cfRule type="expression" dxfId="190" priority="12">
       <formula>$A53="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="189" priority="13">
-      <formula>$A53="blank"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M57">
-    <cfRule type="expression" dxfId="188" priority="14">
+    <cfRule type="expression" dxfId="189" priority="14">
       <formula>$A57="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="187" priority="15">
+    <cfRule type="expression" dxfId="188" priority="15">
       <formula>$A57="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:P14">
+    <cfRule type="expression" dxfId="187" priority="37">
+      <formula>$A5="blank"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="186" priority="36">
       <formula>$A5="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="185" priority="37">
-      <formula>$A5="blank"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P17">
+    <cfRule type="expression" dxfId="185" priority="35">
+      <formula>$A17="blank"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="184" priority="34">
       <formula>$A17="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="183" priority="35">
-      <formula>$A17="blank"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P19:P20">
+    <cfRule type="expression" dxfId="183" priority="33">
+      <formula>$A19="blank"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="182" priority="32">
       <formula>$A19="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="181" priority="33">
-      <formula>$A19="blank"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P22">
+    <cfRule type="expression" dxfId="181" priority="31">
+      <formula>$A22="blank"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="180" priority="30">
       <formula>$A22="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="179" priority="31">
-      <formula>$A22="blank"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P26:P29">
+    <cfRule type="expression" dxfId="179" priority="29">
+      <formula>$A26="blank"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="178" priority="28">
       <formula>$A26="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="177" priority="29">
-      <formula>$A26="blank"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P31:P34">
+    <cfRule type="expression" dxfId="177" priority="25">
+      <formula>$A31="blank"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="176" priority="24">
       <formula>$A31="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="175" priority="25">
-      <formula>$A31="blank"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P37:P39">
-    <cfRule type="expression" dxfId="174" priority="20">
+    <cfRule type="expression" dxfId="175" priority="20">
       <formula>$A37="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="21">
+    <cfRule type="expression" dxfId="174" priority="21">
       <formula>$A37="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P44:P53">
+    <cfRule type="expression" dxfId="173" priority="18">
+      <formula>$A44="header"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="172" priority="19">
       <formula>$A44="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="171" priority="18">
-      <formula>$A44="header"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P57:P66">
+    <cfRule type="expression" dxfId="171" priority="17">
+      <formula>$A57="blank"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="170" priority="16">
       <formula>$A57="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="169" priority="17">
-      <formula>$A57="blank"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P35:Q36">
+    <cfRule type="expression" dxfId="169" priority="116">
+      <formula>$A35="header"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="168" priority="117">
       <formula>$A35="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="167" priority="116">
-      <formula>$A35="header"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q14 P15:Q16 Q17 P18:Q18 Q19:Q20 P21:Q21 Q22 P23:Q25 Q26:Q29 P30:Q30 Q31:Q34 Q37:Q39 P40:Q43 Q44:Q55 P54:Q56 Q57:Q61">
+    <cfRule type="expression" dxfId="167" priority="130">
+      <formula>$A5="blank"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="166" priority="129">
       <formula>$A5="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="165" priority="130">
-      <formula>$A5="blank"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R61">
-    <cfRule type="expression" dxfId="164" priority="11">
+    <cfRule type="expression" dxfId="165" priority="11">
       <formula>$A61="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="163" priority="10">
+    <cfRule type="expression" dxfId="164" priority="10">
       <formula>$A61="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R25:AB56 E35:O35">
-    <cfRule type="expression" dxfId="162" priority="119">
+    <cfRule type="expression" dxfId="163" priority="119">
       <formula>$A25="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="161" priority="118">
+    <cfRule type="expression" dxfId="162" priority="118">
       <formula>$A25="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2">
-    <cfRule type="expression" dxfId="160" priority="4">
+    <cfRule type="expression" dxfId="161" priority="4">
       <formula>$A2="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="159" priority="3">
+    <cfRule type="expression" dxfId="160" priority="3">
       <formula>$A2="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2">
-    <cfRule type="expression" dxfId="158" priority="2">
+    <cfRule type="expression" dxfId="159" priority="2">
       <formula>$A2="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="157" priority="1">
+    <cfRule type="expression" dxfId="158" priority="1">
       <formula>$A2="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:AB2 A2:R2 A3:AB4 A5:M5 O5 R5:AB22 A6:O6 A7:M8 O7:O8 A9:O18 A19:M19 O19 A20:O22 K23:O23 A23:I24 R23:AS24 L24:O24 A25:O34 A35:C35 A36:O38 A39:J39 L39:O39 A40:O52 A53:J53 M53:O53 A54:O56 A57:L57 N57:O57 R57:V57 R58:AB59 A58:O66 S60:AB61 Q62:AB66">
-    <cfRule type="expression" dxfId="156" priority="151">
+    <cfRule type="expression" dxfId="157" priority="151">
       <formula>$A2="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W57">
+    <cfRule type="expression" dxfId="156" priority="138">
+      <formula>$A57="blank"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="155" priority="137">
       <formula>$A57="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="154" priority="138">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X57">
+    <cfRule type="expression" dxfId="154" priority="136">
       <formula>$A57="blank"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X57">
-    <cfRule type="expression" dxfId="153" priority="136">
-      <formula>$A57="blank"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="152" priority="135">
+    <cfRule type="expression" dxfId="153" priority="135">
       <formula>$A57="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y57">
-    <cfRule type="expression" dxfId="151" priority="134">
+    <cfRule type="expression" dxfId="152" priority="134">
       <formula>$A57="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="133">
+    <cfRule type="expression" dxfId="151" priority="133">
       <formula>$A57="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z57:AB57">
+    <cfRule type="expression" dxfId="150" priority="131">
+      <formula>$A57="header"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="149" priority="132">
       <formula>$A57="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="148" priority="131">
-      <formula>$A57="header"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AB2">
-    <cfRule type="expression" dxfId="147" priority="145">
+    <cfRule type="expression" dxfId="148" priority="145">
       <formula>$A2="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="146" priority="146">
+    <cfRule type="expression" dxfId="147" priority="146">
       <formula>$A2="blank"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34598,133 +34603,133 @@
     <mergeCell ref="C1:Y1"/>
   </mergeCells>
   <conditionalFormatting sqref="A2:D2 H2 A3:H30">
-    <cfRule type="expression" dxfId="145" priority="181">
+    <cfRule type="expression" dxfId="146" priority="181">
       <formula>$A2="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:D2 H2:L2 A3:Y4 A5:I5 K5:Y5 A6:Y30">
-    <cfRule type="expression" dxfId="144" priority="182">
+    <cfRule type="expression" dxfId="145" priority="182">
       <formula>$A2="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:Y30 A2:D2 H2:L2 A3:Y4 A5:I5 K5:Y5">
-    <cfRule type="expression" dxfId="143" priority="26">
+    <cfRule type="expression" dxfId="144" priority="26">
       <formula>$A2="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C29">
-    <cfRule type="expression" dxfId="142" priority="184">
+    <cfRule type="expression" dxfId="143" priority="184">
       <formula>#REF!="01"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30">
-    <cfRule type="expression" dxfId="141" priority="10">
+    <cfRule type="expression" dxfId="142" priority="10">
       <formula>#REF!="01"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D29">
+    <cfRule type="cellIs" dxfId="141" priority="190" operator="between">
+      <formula>0</formula>
+      <formula>2</formula>
+    </cfRule>
     <cfRule type="cellIs" dxfId="140" priority="188" operator="between">
       <formula>4</formula>
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="187" operator="between">
+    <cfRule type="cellIs" dxfId="139" priority="186" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="138" priority="187" operator="between">
       <formula>3</formula>
       <formula>3.99999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="186" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="190" operator="between">
-      <formula>0</formula>
-      <formula>2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="189" operator="between">
+    <cfRule type="cellIs" dxfId="137" priority="189" operator="between">
       <formula>2</formula>
       <formula>2.99999</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30">
-    <cfRule type="cellIs" dxfId="135" priority="12" operator="equal">
-      <formula>""</formula>
+    <cfRule type="cellIs" dxfId="136" priority="15" operator="between">
+      <formula>2</formula>
+      <formula>2.99999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="134" priority="13" operator="between">
+    <cfRule type="cellIs" dxfId="135" priority="16" operator="between">
+      <formula>0</formula>
+      <formula>2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="134" priority="14" operator="between">
+      <formula>4</formula>
+      <formula>5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="133" priority="13" operator="between">
       <formula>3</formula>
       <formula>3.99999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="14" operator="between">
-      <formula>4</formula>
-      <formula>5</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="15" operator="between">
-      <formula>2</formula>
-      <formula>2.99999</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="16" operator="between">
-      <formula>0</formula>
-      <formula>2</formula>
+    <cfRule type="cellIs" dxfId="132" priority="12" operator="equal">
+      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:G2">
+    <cfRule type="expression" dxfId="131" priority="23">
+      <formula>$A2="header"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="130" priority="21">
       <formula>$A2="header"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="129" priority="22">
       <formula>$A2="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="128" priority="23">
-      <formula>$A2="header"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:L4 H5:I5 K5:L5 H6:L29">
-    <cfRule type="expression" dxfId="127" priority="185">
+    <cfRule type="expression" dxfId="128" priority="185">
       <formula>#REF!="01"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30:L30">
-    <cfRule type="expression" dxfId="126" priority="11">
+    <cfRule type="expression" dxfId="127" priority="11">
       <formula>#REF!="01"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5">
-    <cfRule type="expression" dxfId="125" priority="5">
-      <formula>#REF!="01"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="124" priority="4">
+    <cfRule type="expression" dxfId="126" priority="4">
       <formula>$A5="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="123" priority="3">
+    <cfRule type="expression" dxfId="125" priority="3">
       <formula>$A5="header"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="124" priority="5">
+      <formula>#REF!="01"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:O2 Q2:S2 Z2:AA2">
-    <cfRule type="expression" dxfId="122" priority="24">
+    <cfRule type="expression" dxfId="123" priority="24">
       <formula>$A2="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="121" priority="25">
+    <cfRule type="expression" dxfId="122" priority="25">
       <formula>$A2="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2">
-    <cfRule type="expression" dxfId="120" priority="1">
+    <cfRule type="expression" dxfId="121" priority="1">
       <formula>$A2="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="119" priority="2">
+    <cfRule type="expression" dxfId="120" priority="2">
       <formula>$A2="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:Y2">
-    <cfRule type="expression" dxfId="118" priority="19">
+    <cfRule type="expression" dxfId="119" priority="19">
       <formula>$A2="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="20">
+    <cfRule type="expression" dxfId="118" priority="20">
       <formula>$A2="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:Y2">
-    <cfRule type="expression" dxfId="116" priority="18">
+    <cfRule type="expression" dxfId="117" priority="18">
       <formula>$A2="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="115" priority="17">
+    <cfRule type="expression" dxfId="116" priority="17">
       <formula>$A2="header"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39210,99 +39215,102 @@
   </mergeCells>
   <phoneticPr fontId="50" type="noConversion"/>
   <conditionalFormatting sqref="A4:H6 A7:C7 E7:H7 A8:H8 A9:C9 E9:H9 A10:H10 A11:C11 E11:H11 A12:G12 A13:C13 E13:G13 A14:H14 A15:C17 E15:H17 A18:H18 A19:C20 E19:H20 A21:H21 A22:C23 E22:H23 A24:H24 A25:C25 E25:G25">
-    <cfRule type="expression" dxfId="114" priority="131">
+    <cfRule type="expression" dxfId="115" priority="131">
       <formula>$A4="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:J4 L4:N4 P4:W4 A5:W6 A7:C7 E7:H7 K7 L7:W15 A8:K8 A9:C9 E9:K9 A10:K10 A11:C11 E11:K11 A12:G12 I12:K12 A13:C13 E13:G13 J13:K14 A14:I14 E15:K15 A15:C17 E16:W17 A18:W18 A19:C20 E19:W20 A21:W21 E22:I22 K22 M22:AN22 A22:C23 L22:L25 E23:K23 M23:W25 A24:K24 A25:C25 E25:G25 I25 K25">
-    <cfRule type="expression" dxfId="113" priority="130">
+    <cfRule type="expression" dxfId="114" priority="130">
       <formula>$A4="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:C15 C17:C19 C22:C25">
-    <cfRule type="expression" dxfId="112" priority="132">
+    <cfRule type="expression" dxfId="113" priority="132">
       <formula>#REF!="01"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="expression" dxfId="111" priority="107">
+    <cfRule type="expression" dxfId="112" priority="107">
       <formula>#REF!="01"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C20">
-    <cfRule type="expression" dxfId="110" priority="91">
+    <cfRule type="expression" dxfId="111" priority="91">
       <formula>#REF!="01"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:G21">
-    <cfRule type="expression" dxfId="109" priority="98">
+    <cfRule type="expression" dxfId="110" priority="98">
       <formula>#REF!="01"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D6 D8 D10 D12 D14 D18 D21 D24">
-    <cfRule type="cellIs" dxfId="108" priority="138" operator="between">
+    <cfRule type="cellIs" dxfId="109" priority="138" operator="between">
       <formula>0</formula>
       <formula>2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="137" operator="between">
+    <cfRule type="cellIs" dxfId="108" priority="137" operator="between">
       <formula>2</formula>
       <formula>2.99999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="136" operator="between">
+    <cfRule type="cellIs" dxfId="107" priority="136" operator="between">
       <formula>4</formula>
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="135" operator="between">
+    <cfRule type="cellIs" dxfId="106" priority="135" operator="between">
       <formula>3</formula>
       <formula>3.99999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="134" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="134" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7">
-    <cfRule type="cellIs" dxfId="103" priority="90" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="90" operator="equal">
       <formula>"Nicht OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="89" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="89" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="88" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="88" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="87">
+    <cfRule type="expression" dxfId="101" priority="87">
       <formula>$A7="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="86">
+    <cfRule type="expression" dxfId="100" priority="86">
       <formula>$A7="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="85">
+    <cfRule type="expression" dxfId="99" priority="85">
       <formula>$A7="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9">
-    <cfRule type="cellIs" dxfId="97" priority="78" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="78" operator="equal">
       <formula>"Nicht OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="77" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="76" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="76" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="75">
+    <cfRule type="expression" dxfId="95" priority="75">
       <formula>$A9="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="74">
+    <cfRule type="expression" dxfId="94" priority="74">
       <formula>$A9="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="73">
+    <cfRule type="expression" dxfId="93" priority="73">
       <formula>$A9="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11">
-    <cfRule type="cellIs" dxfId="91" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="72" operator="equal">
       <formula>"Nicht OK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="91" priority="67">
+      <formula>$A11="header"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="90" priority="71" operator="equal">
       <formula>"OK"</formula>
@@ -39316,146 +39324,146 @@
     <cfRule type="expression" dxfId="87" priority="68">
       <formula>$A11="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="67">
-      <formula>$A11="header"</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D13">
-    <cfRule type="cellIs" dxfId="85" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="66" operator="equal">
       <formula>"Nicht OK"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="61">
+    <cfRule type="cellIs" dxfId="85" priority="64" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="63">
       <formula>$A13="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="62">
+    <cfRule type="cellIs" dxfId="83" priority="65" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="62">
       <formula>$A13="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="63">
+    <cfRule type="expression" dxfId="81" priority="61">
       <formula>$A13="header"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="64" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="65" operator="equal">
-      <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:D17">
-    <cfRule type="expression" dxfId="79" priority="43">
+    <cfRule type="cellIs" dxfId="80" priority="48" operator="equal">
+      <formula>"Nicht OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="79" priority="47" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="78" priority="46" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="44">
+      <formula>$A15="blank"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="43">
       <formula>$A15="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="44">
-      <formula>$A15="blank"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="45">
+    <cfRule type="expression" dxfId="75" priority="45">
       <formula>$A15="header"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="46" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="47" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="48" operator="equal">
-      <formula>"Nicht OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:D20">
-    <cfRule type="expression" dxfId="73" priority="31">
+    <cfRule type="expression" dxfId="74" priority="31">
       <formula>$A19="header"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="34" operator="equal">
+    <cfRule type="expression" dxfId="73" priority="29">
+      <formula>$A19="header"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="30">
+      <formula>$A19="blank"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="71" priority="34" operator="equal">
       <formula>"Nicht OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="33" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="32" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="69" priority="30">
-      <formula>$A19="blank"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="68" priority="29">
-      <formula>$A19="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D21">
-    <cfRule type="cellIs" dxfId="67" priority="104" operator="between">
+    <cfRule type="expression" dxfId="68" priority="35">
+      <formula>#REF!="01"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="36">
+      <formula>#REF!="01"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="101" operator="between">
+      <formula>3</formula>
+      <formula>3.99999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="65" priority="102" operator="between">
+      <formula>4</formula>
+      <formula>5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="100" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="103" operator="between">
+      <formula>2</formula>
+      <formula>2.99999</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="62" priority="104" operator="between">
       <formula>0</formula>
       <formula>2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="35">
-      <formula>#REF!="01"</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:D23">
+    <cfRule type="expression" dxfId="61" priority="17">
+      <formula>$A22="header"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="103" operator="between">
-      <formula>2</formula>
-      <formula>2.99999</formula>
+    <cfRule type="expression" dxfId="60" priority="18">
+      <formula>$A22="blank"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="102" operator="between">
-      <formula>4</formula>
-      <formula>5</formula>
+    <cfRule type="expression" dxfId="59" priority="19">
+      <formula>$A22="header"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="101" operator="between">
-      <formula>3</formula>
-      <formula>3.99999</formula>
+    <cfRule type="cellIs" dxfId="58" priority="21" operator="equal">
+      <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="100" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="22" operator="equal">
+      <formula>"Nicht OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="56" priority="20" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D22:D23">
-    <cfRule type="cellIs" dxfId="61" priority="22" operator="equal">
+  <conditionalFormatting sqref="D25">
+    <cfRule type="expression" dxfId="55" priority="11">
+      <formula>$A25="header"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="54" priority="15" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="53" priority="16" operator="equal">
       <formula>"Nicht OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="21" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="20" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="19">
-      <formula>$A22="header"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="57" priority="18">
-      <formula>$A22="blank"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="56" priority="17">
-      <formula>$A22="header"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D25">
-    <cfRule type="expression" dxfId="55" priority="12">
+    <cfRule type="expression" dxfId="52" priority="12">
       <formula>$A25="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="11">
+    <cfRule type="expression" dxfId="51" priority="13">
       <formula>$A25="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="13">
-      <formula>$A25="header"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="14" operator="equal">
       <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="15" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="16" operator="equal">
-      <formula>"Nicht OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12:H13">
     <cfRule type="expression" dxfId="49" priority="114">
       <formula>$A12="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="115">
-      <formula>$A12="blank"</formula>
+    <cfRule type="expression" dxfId="48" priority="117">
+      <formula>#REF!="01"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="47" priority="116">
       <formula>$A12="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="117">
-      <formula>#REF!="01"</formula>
+    <cfRule type="expression" dxfId="46" priority="115">
+      <formula>$A12="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
@@ -39464,17 +39472,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="expression" dxfId="44" priority="3">
-      <formula>$A25="header"</formula>
+    <cfRule type="expression" dxfId="44" priority="6">
+      <formula>#REF!="01"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="43" priority="4">
       <formula>$A25="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="5">
+    <cfRule type="expression" dxfId="42" priority="3">
       <formula>$A25="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="6">
-      <formula>#REF!="01"</formula>
+    <cfRule type="expression" dxfId="41" priority="5">
+      <formula>$A25="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:I6 H7:H8 H9:I10 I12 H14 H15:I15 I16:I17 H17 H18:I19 H22:I24 I25">
@@ -39493,57 +39501,57 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="expression" dxfId="37" priority="121">
-      <formula>$A7="header"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="122">
+    <cfRule type="expression" dxfId="37" priority="122">
       <formula>$A7="blank"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="123">
+    <cfRule type="expression" dxfId="36" priority="123">
       <formula>#REF!="01"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="121">
+      <formula>$A7="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7">
-    <cfRule type="expression" dxfId="34" priority="120">
+    <cfRule type="expression" dxfId="34" priority="119">
+      <formula>$A7="header"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="120">
       <formula>$A7="blank"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="119">
-      <formula>$A7="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J22">
-    <cfRule type="expression" dxfId="32" priority="124">
+    <cfRule type="expression" dxfId="32" priority="125">
+      <formula>$A22="blank"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="124">
       <formula>$A22="header"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="125">
-      <formula>$A22="blank"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="30" priority="126">
       <formula>#REF!="01"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J25">
-    <cfRule type="expression" dxfId="29" priority="2">
+    <cfRule type="expression" dxfId="29" priority="1">
+      <formula>$A25="header"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="2">
       <formula>$A25="blank"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="1">
-      <formula>$A25="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="expression" dxfId="27" priority="8">
+    <cfRule type="expression" dxfId="27" priority="7">
+      <formula>$A4="header"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="8">
       <formula>$A4="blank"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="7">
-      <formula>$A4="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4">
-    <cfRule type="expression" dxfId="25" priority="9">
+    <cfRule type="expression" dxfId="25" priority="10">
+      <formula>$A4="blank"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="9">
       <formula>$A4="header"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="10">
-      <formula>$A4="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:W4 A21:W21 A4:J4 L4:N4 A5:W6 A7:C7 E7:H7 K7 L7:W15 A8:K8 A9:C9 E9:K9 A10:K10 A11:C11 E11:K11 A12:G12 I12:K12 A13:C13 E13:G13 J13:K14 A14:I14 E15:K15 A15:C17 E16:W17 A18:W18 A19:C20 E19:W20 E22:I22 K22 M22:AN22 A22:C23 L22:L25 E23:K23 M23:W25 A24:K24 A25:C25 E25:G25 I25 K25">
@@ -39552,11 +39560,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V4:W4">
-    <cfRule type="expression" dxfId="22" priority="127">
+    <cfRule type="expression" dxfId="22" priority="128">
+      <formula>$A4="blank"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="127">
       <formula>$A4="header"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="128">
-      <formula>$A4="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -39609,13 +39617,13 @@
   <sheetData>
     <row r="1" spans="1:20" s="216" customFormat="1" ht="60" customHeight="1">
       <c r="A1" s="210"/>
-      <c r="B1" s="377" t="s">
+      <c r="B1" s="387" t="s">
         <v>1284</v>
       </c>
-      <c r="C1" s="378"/>
-      <c r="D1" s="378"/>
-      <c r="E1" s="378"/>
-      <c r="F1" s="378"/>
+      <c r="C1" s="386"/>
+      <c r="D1" s="386"/>
+      <c r="E1" s="386"/>
+      <c r="F1" s="386"/>
       <c r="H1" s="252"/>
       <c r="I1" s="253"/>
       <c r="J1" s="254"/>
@@ -39728,10 +39736,10 @@
     </row>
     <row r="6" spans="1:20" s="269" customFormat="1" ht="30.75" customHeight="1">
       <c r="A6" s="191"/>
-      <c r="B6" s="379" t="s">
+      <c r="B6" s="380" t="s">
         <v>650</v>
       </c>
-      <c r="C6" s="380"/>
+      <c r="C6" s="381"/>
       <c r="D6" s="270" t="str">
         <f>J106</f>
         <v/>
@@ -39821,13 +39829,13 @@
     </row>
     <row r="19" spans="1:40" s="216" customFormat="1" ht="60" customHeight="1">
       <c r="A19" s="210"/>
-      <c r="B19" s="381" t="s">
+      <c r="B19" s="388" t="s">
         <v>654</v>
       </c>
-      <c r="C19" s="381"/>
-      <c r="D19" s="381"/>
-      <c r="E19" s="381"/>
-      <c r="F19" s="381"/>
+      <c r="C19" s="388"/>
+      <c r="D19" s="388"/>
+      <c r="E19" s="388"/>
+      <c r="F19" s="388"/>
       <c r="H19" s="252"/>
       <c r="I19" s="253"/>
       <c r="J19" s="254"/>
@@ -39861,10 +39869,10 @@
       <c r="AN19" s="254"/>
     </row>
     <row r="20" spans="1:40" ht="33" customHeight="1">
-      <c r="B20" s="379" t="s">
+      <c r="B20" s="380" t="s">
         <v>650</v>
       </c>
-      <c r="C20" s="380"/>
+      <c r="C20" s="381"/>
       <c r="D20" s="289" t="str">
         <f>J69</f>
         <v/>
@@ -40006,13 +40014,13 @@
       <c r="B23" s="302" t="s">
         <v>194</v>
       </c>
-      <c r="C23" s="385" t="str">
+      <c r="C23" s="377" t="str">
         <f>VLOOKUP(B23,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent are information security policies available?</v>
       </c>
-      <c r="D23" s="386"/>
-      <c r="E23" s="386"/>
-      <c r="F23" s="387"/>
+      <c r="D23" s="378"/>
+      <c r="E23" s="378"/>
+      <c r="F23" s="379"/>
       <c r="G23" s="303">
         <f t="shared" ref="G23:G68" si="0">IF(H23="na","na",3)</f>
         <v>3</v>
@@ -40060,13 +40068,13 @@
       <c r="B24" s="302" t="s">
         <v>204</v>
       </c>
-      <c r="C24" s="385" t="str">
+      <c r="C24" s="377" t="str">
         <f>VLOOKUP(B24,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is information security managed within the organization?</v>
       </c>
-      <c r="D24" s="386"/>
-      <c r="E24" s="386"/>
-      <c r="F24" s="387"/>
+      <c r="D24" s="378"/>
+      <c r="E24" s="378"/>
+      <c r="F24" s="379"/>
       <c r="G24" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -40114,13 +40122,13 @@
       <c r="B25" s="302" t="s">
         <v>210</v>
       </c>
-      <c r="C25" s="385" t="str">
+      <c r="C25" s="377" t="str">
         <f>VLOOKUP(B25,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent are information security responsibilities organized?</v>
       </c>
-      <c r="D25" s="386"/>
-      <c r="E25" s="386"/>
-      <c r="F25" s="387"/>
+      <c r="D25" s="378"/>
+      <c r="E25" s="378"/>
+      <c r="F25" s="379"/>
       <c r="G25" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -40175,13 +40183,13 @@
       <c r="B26" s="302" t="s">
         <v>216</v>
       </c>
-      <c r="C26" s="385" t="str">
+      <c r="C26" s="377" t="str">
         <f>VLOOKUP(B26,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent are information security requirements considered in projects?</v>
       </c>
-      <c r="D26" s="386"/>
-      <c r="E26" s="386"/>
-      <c r="F26" s="387"/>
+      <c r="D26" s="378"/>
+      <c r="E26" s="378"/>
+      <c r="F26" s="379"/>
       <c r="G26" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -40236,13 +40244,13 @@
       <c r="B27" s="302" t="s">
         <v>222</v>
       </c>
-      <c r="C27" s="385" t="str">
+      <c r="C27" s="377" t="str">
         <f>VLOOKUP(B27,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent are the responsibilities between external IT service providers and the own organization defined?</v>
       </c>
-      <c r="D27" s="386"/>
-      <c r="E27" s="386"/>
-      <c r="F27" s="387"/>
+      <c r="D27" s="378"/>
+      <c r="E27" s="378"/>
+      <c r="F27" s="379"/>
       <c r="G27" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -40297,13 +40305,13 @@
       <c r="B28" s="302" t="s">
         <v>230</v>
       </c>
-      <c r="C28" s="385" t="str">
+      <c r="C28" s="377" t="str">
         <f>VLOOKUP(B28,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v xml:space="preserve">To what extent are information assets identified and recorded? </v>
       </c>
-      <c r="D28" s="386"/>
-      <c r="E28" s="386"/>
-      <c r="F28" s="387"/>
+      <c r="D28" s="378"/>
+      <c r="E28" s="378"/>
+      <c r="F28" s="379"/>
       <c r="G28" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -40358,13 +40366,13 @@
       <c r="B29" s="302" t="s">
         <v>234</v>
       </c>
-      <c r="C29" s="385" t="str">
+      <c r="C29" s="377" t="str">
         <f>VLOOKUP(B29,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent are information assets classified and managed in terms of their protection needs?</v>
       </c>
-      <c r="D29" s="386"/>
-      <c r="E29" s="386"/>
-      <c r="F29" s="387"/>
+      <c r="D29" s="378"/>
+      <c r="E29" s="378"/>
+      <c r="F29" s="379"/>
       <c r="G29" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -40419,13 +40427,13 @@
       <c r="B30" s="302" t="s">
         <v>238</v>
       </c>
-      <c r="C30" s="385" t="str">
+      <c r="C30" s="377" t="str">
         <f>VLOOKUP(B30,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is it ensured that only evaluated and approved external IT services are used for processing the organization’s information assets?</v>
       </c>
-      <c r="D30" s="386"/>
-      <c r="E30" s="386"/>
-      <c r="F30" s="387"/>
+      <c r="D30" s="378"/>
+      <c r="E30" s="378"/>
+      <c r="F30" s="379"/>
       <c r="G30" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -40480,13 +40488,13 @@
       <c r="B31" s="310" t="s">
         <v>244</v>
       </c>
-      <c r="C31" s="385" t="str">
+      <c r="C31" s="377" t="str">
         <f>VLOOKUP(B31,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is it ensured that only evaluated and approved software is used for processing the organization’s information assets?</v>
       </c>
-      <c r="D31" s="386"/>
-      <c r="E31" s="386"/>
-      <c r="F31" s="387"/>
+      <c r="D31" s="378"/>
+      <c r="E31" s="378"/>
+      <c r="F31" s="379"/>
       <c r="G31" s="303">
         <f t="shared" ref="G31" si="2">IF(H31="na","na",3)</f>
         <v>3</v>
@@ -40542,13 +40550,13 @@
       <c r="B32" s="302" t="s">
         <v>256</v>
       </c>
-      <c r="C32" s="385" t="str">
+      <c r="C32" s="377" t="str">
         <f>VLOOKUP(B32,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent are information security risks managed?</v>
       </c>
-      <c r="D32" s="386"/>
-      <c r="E32" s="386"/>
-      <c r="F32" s="387"/>
+      <c r="D32" s="378"/>
+      <c r="E32" s="378"/>
+      <c r="F32" s="379"/>
       <c r="G32" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -40605,13 +40613,13 @@
       <c r="B33" s="302" t="s">
         <v>264</v>
       </c>
-      <c r="C33" s="385" t="str">
+      <c r="C33" s="377" t="str">
         <f>VLOOKUP(B33,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is compliance with information security ensured in procedures and processes?</v>
       </c>
-      <c r="D33" s="386"/>
-      <c r="E33" s="386"/>
-      <c r="F33" s="387"/>
+      <c r="D33" s="378"/>
+      <c r="E33" s="378"/>
+      <c r="F33" s="379"/>
       <c r="G33" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -40659,13 +40667,13 @@
       <c r="B34" s="302" t="s">
         <v>270</v>
       </c>
-      <c r="C34" s="385" t="str">
+      <c r="C34" s="377" t="str">
         <f>VLOOKUP(B34,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is the ISMS reviewed by an independent authority?</v>
       </c>
-      <c r="D34" s="386"/>
-      <c r="E34" s="386"/>
-      <c r="F34" s="387"/>
+      <c r="D34" s="378"/>
+      <c r="E34" s="378"/>
+      <c r="F34" s="379"/>
       <c r="G34" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -40713,13 +40721,13 @@
       <c r="B35" s="302" t="s">
         <v>276</v>
       </c>
-      <c r="C35" s="385" t="str">
+      <c r="C35" s="377" t="str">
         <f>VLOOKUP(B35,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent are information security relevant events or observations reported?</v>
       </c>
-      <c r="D35" s="386"/>
-      <c r="E35" s="386"/>
-      <c r="F35" s="387"/>
+      <c r="D35" s="378"/>
+      <c r="E35" s="378"/>
+      <c r="F35" s="379"/>
       <c r="G35" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -40774,14 +40782,14 @@
       <c r="B36" s="302" t="s">
         <v>279</v>
       </c>
-      <c r="C36" s="385" t="str">
+      <c r="C36" s="377" t="str">
         <f>VLOOKUP(B36,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v xml:space="preserve">To what extent are reported security events managed?
 </v>
       </c>
-      <c r="D36" s="386"/>
-      <c r="E36" s="386"/>
-      <c r="F36" s="387"/>
+      <c r="D36" s="378"/>
+      <c r="E36" s="378"/>
+      <c r="F36" s="379"/>
       <c r="G36" s="303">
         <f t="shared" ref="G36:G37" si="3">IF(H36="na","na",3)</f>
         <v>3</v>
@@ -40836,14 +40844,14 @@
       <c r="B37" s="302" t="s">
         <v>286</v>
       </c>
-      <c r="C37" s="385" t="str">
+      <c r="C37" s="377" t="str">
         <f>VLOOKUP(B37,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v xml:space="preserve">To what extent is the organization prepared to handle crisis situations?
 </v>
       </c>
-      <c r="D37" s="386"/>
-      <c r="E37" s="386"/>
-      <c r="F37" s="387"/>
+      <c r="D37" s="378"/>
+      <c r="E37" s="378"/>
+      <c r="F37" s="379"/>
       <c r="G37" s="303">
         <f t="shared" si="3"/>
         <v>3</v>
@@ -40898,13 +40906,13 @@
       <c r="B38" s="302" t="s">
         <v>293</v>
       </c>
-      <c r="C38" s="385" t="str">
+      <c r="C38" s="377" t="str">
         <f>VLOOKUP(B38,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is the qualification of employees for sensitive work fields ensured?</v>
       </c>
-      <c r="D38" s="386"/>
-      <c r="E38" s="386"/>
-      <c r="F38" s="387"/>
+      <c r="D38" s="378"/>
+      <c r="E38" s="378"/>
+      <c r="F38" s="379"/>
       <c r="G38" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -40960,13 +40968,13 @@
       <c r="B39" s="302" t="s">
         <v>298</v>
       </c>
-      <c r="C39" s="385" t="str">
+      <c r="C39" s="377" t="str">
         <f>VLOOKUP(B39,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is all staff contractually bound to comply with information security policies?</v>
       </c>
-      <c r="D39" s="386"/>
-      <c r="E39" s="386"/>
-      <c r="F39" s="387"/>
+      <c r="D39" s="378"/>
+      <c r="E39" s="378"/>
+      <c r="F39" s="379"/>
       <c r="G39" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -41018,13 +41026,13 @@
       <c r="B40" s="302" t="s">
         <v>304</v>
       </c>
-      <c r="C40" s="385" t="str">
+      <c r="C40" s="377" t="str">
         <f>VLOOKUP(B40,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is staff made aware of and trained with respect to the risks arising from the handling of information?</v>
       </c>
-      <c r="D40" s="386"/>
-      <c r="E40" s="386"/>
-      <c r="F40" s="387"/>
+      <c r="D40" s="378"/>
+      <c r="E40" s="378"/>
+      <c r="F40" s="379"/>
       <c r="G40" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -41079,13 +41087,13 @@
       <c r="B41" s="302" t="s">
         <v>309</v>
       </c>
-      <c r="C41" s="385" t="str">
+      <c r="C41" s="377" t="str">
         <f>VLOOKUP(B41,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is mobile work regulated?</v>
       </c>
-      <c r="D41" s="386"/>
-      <c r="E41" s="386"/>
-      <c r="F41" s="387"/>
+      <c r="D41" s="378"/>
+      <c r="E41" s="378"/>
+      <c r="F41" s="379"/>
       <c r="G41" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -41141,13 +41149,13 @@
       <c r="B42" s="302" t="s">
         <v>318</v>
       </c>
-      <c r="C42" s="385" t="str">
+      <c r="C42" s="377" t="str">
         <f>VLOOKUP(B42,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent are security zones managed to protect information assets?</v>
       </c>
-      <c r="D42" s="386"/>
-      <c r="E42" s="386"/>
-      <c r="F42" s="387"/>
+      <c r="D42" s="378"/>
+      <c r="E42" s="378"/>
+      <c r="F42" s="379"/>
       <c r="G42" s="303">
         <f>IF(H42="na","na",3)</f>
         <v>3</v>
@@ -41202,13 +41210,13 @@
       <c r="B43" s="302" t="s">
         <v>325</v>
       </c>
-      <c r="C43" s="385" t="str">
+      <c r="C43" s="377" t="str">
         <f>VLOOKUP(B43,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>Superseded by 1.6.3, 5.2.8 and 5.2.9</v>
       </c>
-      <c r="D43" s="386"/>
-      <c r="E43" s="386"/>
-      <c r="F43" s="387"/>
+      <c r="D43" s="378"/>
+      <c r="E43" s="378"/>
+      <c r="F43" s="379"/>
       <c r="G43" s="303" t="str">
         <f t="shared" si="0"/>
         <v>na</v>
@@ -41262,13 +41270,13 @@
       <c r="B44" s="302" t="s">
         <v>328</v>
       </c>
-      <c r="C44" s="385" t="str">
+      <c r="C44" s="377" t="str">
         <f>VLOOKUP(B44,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is the handling of supporting assets managed?</v>
       </c>
-      <c r="D44" s="386"/>
-      <c r="E44" s="386"/>
-      <c r="F44" s="387"/>
+      <c r="D44" s="378"/>
+      <c r="E44" s="378"/>
+      <c r="F44" s="379"/>
       <c r="G44" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -41323,13 +41331,13 @@
       <c r="B45" s="302" t="s">
         <v>334</v>
       </c>
-      <c r="C45" s="385" t="str">
+      <c r="C45" s="377" t="str">
         <f>VLOOKUP(B45,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is the handling of mobile IT devices and mobile data storage devices managed?</v>
       </c>
-      <c r="D45" s="386"/>
-      <c r="E45" s="386"/>
-      <c r="F45" s="387"/>
+      <c r="D45" s="378"/>
+      <c r="E45" s="378"/>
+      <c r="F45" s="379"/>
       <c r="G45" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -41385,13 +41393,13 @@
       <c r="B46" s="302" t="s">
         <v>345</v>
       </c>
-      <c r="C46" s="385" t="str">
+      <c r="C46" s="377" t="str">
         <f>VLOOKUP(B46,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is the use of identification means managed?</v>
       </c>
-      <c r="D46" s="386"/>
-      <c r="E46" s="386"/>
-      <c r="F46" s="387"/>
+      <c r="D46" s="378"/>
+      <c r="E46" s="378"/>
+      <c r="F46" s="379"/>
       <c r="G46" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -41446,13 +41454,13 @@
       <c r="B47" s="302" t="s">
         <v>351</v>
       </c>
-      <c r="C47" s="385" t="str">
+      <c r="C47" s="377" t="str">
         <f>VLOOKUP(B47,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is the user access to IT services and IT systems secured?</v>
       </c>
-      <c r="D47" s="386"/>
-      <c r="E47" s="386"/>
-      <c r="F47" s="387"/>
+      <c r="D47" s="378"/>
+      <c r="E47" s="378"/>
+      <c r="F47" s="379"/>
       <c r="G47" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -41507,13 +41515,13 @@
       <c r="B48" s="302" t="s">
         <v>356</v>
       </c>
-      <c r="C48" s="385" t="str">
+      <c r="C48" s="377" t="str">
         <f>VLOOKUP(B48,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v xml:space="preserve">To what extent are user accounts and login information securely managed and applied? </v>
       </c>
-      <c r="D48" s="386"/>
-      <c r="E48" s="386"/>
-      <c r="F48" s="387"/>
+      <c r="D48" s="378"/>
+      <c r="E48" s="378"/>
+      <c r="F48" s="379"/>
       <c r="G48" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -41568,13 +41576,13 @@
       <c r="B49" s="302" t="s">
         <v>363</v>
       </c>
-      <c r="C49" s="385" t="str">
+      <c r="C49" s="377" t="str">
         <f>VLOOKUP(B49,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent are access rights assigned and managed?</v>
       </c>
-      <c r="D49" s="386"/>
-      <c r="E49" s="386"/>
-      <c r="F49" s="387"/>
+      <c r="D49" s="378"/>
+      <c r="E49" s="378"/>
+      <c r="F49" s="379"/>
       <c r="G49" s="303">
         <f>IF(H49="na","na",3)</f>
         <v>3</v>
@@ -41629,13 +41637,13 @@
       <c r="B50" s="302" t="s">
         <v>373</v>
       </c>
-      <c r="C50" s="385" t="str">
+      <c r="C50" s="377" t="str">
         <f>VLOOKUP(B50,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is the use of cryptographic procedures managed?</v>
       </c>
-      <c r="D50" s="386"/>
-      <c r="E50" s="386"/>
-      <c r="F50" s="387"/>
+      <c r="D50" s="378"/>
+      <c r="E50" s="378"/>
+      <c r="F50" s="379"/>
       <c r="G50" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -41693,13 +41701,13 @@
       <c r="B51" s="302" t="s">
         <v>378</v>
       </c>
-      <c r="C51" s="385" t="str">
+      <c r="C51" s="377" t="str">
         <f>VLOOKUP(B51,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is information protected during transfer?</v>
       </c>
-      <c r="D51" s="386"/>
-      <c r="E51" s="386"/>
-      <c r="F51" s="387"/>
+      <c r="D51" s="378"/>
+      <c r="E51" s="378"/>
+      <c r="F51" s="379"/>
       <c r="G51" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -41757,13 +41765,13 @@
       <c r="B52" s="302" t="s">
         <v>389</v>
       </c>
-      <c r="C52" s="385" t="str">
+      <c r="C52" s="377" t="str">
         <f>VLOOKUP(B52,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v xml:space="preserve">To what extent are changes managed? </v>
       </c>
-      <c r="D52" s="386"/>
-      <c r="E52" s="386"/>
-      <c r="F52" s="387"/>
+      <c r="D52" s="378"/>
+      <c r="E52" s="378"/>
+      <c r="F52" s="379"/>
       <c r="G52" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -41822,13 +41830,13 @@
       <c r="B53" s="302" t="s">
         <v>394</v>
       </c>
-      <c r="C53" s="385" t="str">
+      <c r="C53" s="377" t="str">
         <f>VLOOKUP(B53,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent are development and testing environments separated from operational environments?</v>
       </c>
-      <c r="D53" s="386"/>
-      <c r="E53" s="386"/>
-      <c r="F53" s="387"/>
+      <c r="D53" s="378"/>
+      <c r="E53" s="378"/>
+      <c r="F53" s="379"/>
       <c r="G53" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -41886,13 +41894,13 @@
       <c r="B54" s="302" t="s">
         <v>399</v>
       </c>
-      <c r="C54" s="385" t="str">
+      <c r="C54" s="377" t="str">
         <f>VLOOKUP(B54,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent are IT systems protected against malware?</v>
       </c>
-      <c r="D54" s="386"/>
-      <c r="E54" s="386"/>
-      <c r="F54" s="387"/>
+      <c r="D54" s="378"/>
+      <c r="E54" s="378"/>
+      <c r="F54" s="379"/>
       <c r="G54" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -41950,13 +41958,13 @@
       <c r="B55" s="302" t="s">
         <v>405</v>
       </c>
-      <c r="C55" s="385" t="str">
+      <c r="C55" s="377" t="str">
         <f>VLOOKUP(B55,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent are event logs recorded and analysed?</v>
       </c>
-      <c r="D55" s="386"/>
-      <c r="E55" s="386"/>
-      <c r="F55" s="387"/>
+      <c r="D55" s="378"/>
+      <c r="E55" s="378"/>
+      <c r="F55" s="379"/>
       <c r="G55" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -42001,13 +42009,13 @@
       <c r="B56" s="302" t="s">
         <v>412</v>
       </c>
-      <c r="C56" s="385" t="str">
+      <c r="C56" s="377" t="str">
         <f>VLOOKUP(B56,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v xml:space="preserve">To what extent are vulnerabilities identified and addressed? </v>
       </c>
-      <c r="D56" s="386"/>
-      <c r="E56" s="386"/>
-      <c r="F56" s="387"/>
+      <c r="D56" s="378"/>
+      <c r="E56" s="378"/>
+      <c r="F56" s="379"/>
       <c r="G56" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -42052,13 +42060,13 @@
       <c r="B57" s="302" t="s">
         <v>417</v>
       </c>
-      <c r="C57" s="385" t="str">
+      <c r="C57" s="377" t="str">
         <f>VLOOKUP(B57,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent are IT systems and services technically checked (system and service audit)?</v>
       </c>
-      <c r="D57" s="386"/>
-      <c r="E57" s="386"/>
-      <c r="F57" s="387"/>
+      <c r="D57" s="378"/>
+      <c r="E57" s="378"/>
+      <c r="F57" s="379"/>
       <c r="G57" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -42103,14 +42111,14 @@
       <c r="B58" s="302" t="s">
         <v>422</v>
       </c>
-      <c r="C58" s="385" t="str">
+      <c r="C58" s="377" t="str">
         <f>VLOOKUP(B58,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v xml:space="preserve">To what extent is the network of the organization managed?
 </v>
       </c>
-      <c r="D58" s="386"/>
-      <c r="E58" s="386"/>
-      <c r="F58" s="387"/>
+      <c r="D58" s="378"/>
+      <c r="E58" s="378"/>
+      <c r="F58" s="379"/>
       <c r="G58" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -42155,13 +42163,13 @@
       <c r="B59" s="302" t="s">
         <v>429</v>
       </c>
-      <c r="C59" s="385" t="str">
+      <c r="C59" s="377" t="str">
         <f>VLOOKUP(B59,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is continuity planning for IT services in place?</v>
       </c>
-      <c r="D59" s="386"/>
-      <c r="E59" s="386"/>
-      <c r="F59" s="387"/>
+      <c r="D59" s="378"/>
+      <c r="E59" s="378"/>
+      <c r="F59" s="379"/>
       <c r="G59" s="303">
         <f t="shared" ref="G59:G60" si="4">IF(H59="na","na",3)</f>
         <v>3</v>
@@ -42209,13 +42217,13 @@
       <c r="B60" s="302" t="s">
         <v>436</v>
       </c>
-      <c r="C60" s="385" t="str">
+      <c r="C60" s="377" t="str">
         <f>VLOOKUP(B60,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is the backup and recovery of data and IT services ensured?</v>
       </c>
-      <c r="D60" s="386"/>
-      <c r="E60" s="386"/>
-      <c r="F60" s="387"/>
+      <c r="D60" s="378"/>
+      <c r="E60" s="378"/>
+      <c r="F60" s="379"/>
       <c r="G60" s="303">
         <f t="shared" si="4"/>
         <v>3</v>
@@ -42263,13 +42271,13 @@
       <c r="B61" s="302" t="s">
         <v>442</v>
       </c>
-      <c r="C61" s="385" t="str">
+      <c r="C61" s="377" t="str">
         <f>VLOOKUP(B61,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is information security considered in new or further developed IT systems?</v>
       </c>
-      <c r="D61" s="386"/>
-      <c r="E61" s="386"/>
-      <c r="F61" s="387"/>
+      <c r="D61" s="378"/>
+      <c r="E61" s="378"/>
+      <c r="F61" s="379"/>
       <c r="G61" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -42317,13 +42325,13 @@
       <c r="B62" s="302" t="s">
         <v>446</v>
       </c>
-      <c r="C62" s="385" t="str">
+      <c r="C62" s="377" t="str">
         <f>VLOOKUP(B62,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent are requirements for network services defined?</v>
       </c>
-      <c r="D62" s="386"/>
-      <c r="E62" s="386"/>
-      <c r="F62" s="387"/>
+      <c r="D62" s="378"/>
+      <c r="E62" s="378"/>
+      <c r="F62" s="379"/>
       <c r="G62" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -42372,13 +42380,13 @@
       <c r="B63" s="302" t="s">
         <v>453</v>
       </c>
-      <c r="C63" s="385" t="str">
+      <c r="C63" s="377" t="str">
         <f>VLOOKUP(B63,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v xml:space="preserve">To what extent is the return and secure removal of information assets from external IT services regulated? </v>
       </c>
-      <c r="D63" s="386"/>
-      <c r="E63" s="386"/>
-      <c r="F63" s="387"/>
+      <c r="D63" s="378"/>
+      <c r="E63" s="378"/>
+      <c r="F63" s="379"/>
       <c r="G63" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -42426,13 +42434,13 @@
       <c r="B64" s="302" t="s">
         <v>458</v>
       </c>
-      <c r="C64" s="385" t="str">
+      <c r="C64" s="377" t="str">
         <f>VLOOKUP(B64,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is information protected in shared external IT services?</v>
       </c>
-      <c r="D64" s="386"/>
-      <c r="E64" s="386"/>
-      <c r="F64" s="387"/>
+      <c r="D64" s="378"/>
+      <c r="E64" s="378"/>
+      <c r="F64" s="379"/>
       <c r="G64" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -42480,14 +42488,14 @@
       <c r="B65" s="302" t="s">
         <v>464</v>
       </c>
-      <c r="C65" s="385" t="str">
+      <c r="C65" s="377" t="str">
         <f>VLOOKUP(B65,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v xml:space="preserve">To what extent is information security ensured among contractors and cooperation partners?
 </v>
       </c>
-      <c r="D65" s="386"/>
-      <c r="E65" s="386"/>
-      <c r="F65" s="387"/>
+      <c r="D65" s="378"/>
+      <c r="E65" s="378"/>
+      <c r="F65" s="379"/>
       <c r="G65" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -42535,13 +42543,13 @@
       <c r="B66" s="302" t="s">
         <v>475</v>
       </c>
-      <c r="C66" s="385" t="str">
+      <c r="C66" s="377" t="str">
         <f>VLOOKUP(B66,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is non-disclosure regarding the exchange of information contractually agreed?</v>
       </c>
-      <c r="D66" s="386"/>
-      <c r="E66" s="386"/>
-      <c r="F66" s="387"/>
+      <c r="D66" s="378"/>
+      <c r="E66" s="378"/>
+      <c r="F66" s="379"/>
       <c r="G66" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -42589,13 +42597,13 @@
       <c r="B67" s="302" t="s">
         <v>481</v>
       </c>
-      <c r="C67" s="385" t="str">
+      <c r="C67" s="377" t="str">
         <f>VLOOKUP(B67,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v>To what extent is compliance with regulatory and contractual provisions ensured?</v>
       </c>
-      <c r="D67" s="386"/>
-      <c r="E67" s="386"/>
-      <c r="F67" s="387"/>
+      <c r="D67" s="378"/>
+      <c r="E67" s="378"/>
+      <c r="F67" s="379"/>
       <c r="G67" s="303">
         <f>IF(H67="na","na",3)</f>
         <v>3</v>
@@ -42643,13 +42651,13 @@
       <c r="B68" s="302" t="s">
         <v>486</v>
       </c>
-      <c r="C68" s="385" t="str">
+      <c r="C68" s="377" t="str">
         <f>VLOOKUP(B68,'Information Security'!$C$3:$H$66,6,FALSE)</f>
         <v xml:space="preserve">To what extent is the protection of personally identifiable data considered when implementing information security? </v>
       </c>
-      <c r="D68" s="386"/>
-      <c r="E68" s="386"/>
-      <c r="F68" s="387"/>
+      <c r="D68" s="378"/>
+      <c r="E68" s="378"/>
+      <c r="F68" s="379"/>
       <c r="G68" s="303">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -42845,13 +42853,13 @@
       <c r="AN72" s="278"/>
     </row>
     <row r="73" spans="1:40" ht="60" customHeight="1">
-      <c r="B73" s="388" t="s">
+      <c r="B73" s="385" t="s">
         <v>689</v>
       </c>
-      <c r="C73" s="378"/>
-      <c r="D73" s="378"/>
-      <c r="E73" s="378"/>
-      <c r="F73" s="378"/>
+      <c r="C73" s="386"/>
+      <c r="D73" s="386"/>
+      <c r="E73" s="386"/>
+      <c r="F73" s="386"/>
       <c r="G73" s="216"/>
       <c r="H73" s="252"/>
       <c r="R73" s="291"/>
@@ -42879,10 +42887,10 @@
       <c r="AN73" s="278"/>
     </row>
     <row r="74" spans="1:40" ht="33.75" customHeight="1">
-      <c r="B74" s="379" t="s">
+      <c r="B74" s="380" t="s">
         <v>650</v>
       </c>
-      <c r="C74" s="380"/>
+      <c r="C74" s="381"/>
       <c r="D74" s="270" t="str">
         <f>J104</f>
         <v/>
@@ -47803,6 +47811,45 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C55:F55"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="C68:F68"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="C58:F58"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="C64:F64"/>
+    <mergeCell ref="C67:F67"/>
+    <mergeCell ref="C65:F65"/>
+    <mergeCell ref="C66:F66"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="C47:F47"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="C51:F51"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="C37:F37"/>
@@ -47819,45 +47866,6 @@
     <mergeCell ref="C56:F56"/>
     <mergeCell ref="C44:F44"/>
     <mergeCell ref="C45:F45"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="C47:F47"/>
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="C50:F50"/>
-    <mergeCell ref="C51:F51"/>
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="C68:F68"/>
-    <mergeCell ref="C57:F57"/>
-    <mergeCell ref="C58:F58"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="C62:F62"/>
-    <mergeCell ref="C63:F63"/>
-    <mergeCell ref="C64:F64"/>
-    <mergeCell ref="C67:F67"/>
-    <mergeCell ref="C65:F65"/>
-    <mergeCell ref="C66:F66"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="C76:F76"/>
-    <mergeCell ref="B110:F110"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C55:F55"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="C22:F22"/>
   </mergeCells>
   <phoneticPr fontId="50" type="noConversion"/>
   <conditionalFormatting sqref="D6">
@@ -47875,13 +47883,13 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D20">
-    <cfRule type="cellIs" dxfId="17" priority="24" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="17" priority="25" stopIfTrue="1" operator="between">
+      <formula>G20 * 0.7</formula>
+      <formula>G20 * 0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="24" stopIfTrue="1" operator="between">
       <formula>0</formula>
       <formula>G20 * 0.7</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="25" stopIfTrue="1" operator="between">
-      <formula>G20 * 0.7</formula>
-      <formula>G20 * 0.9</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="15" priority="26" stopIfTrue="1" operator="between">
       <formula>G20 * 0.9</formula>
@@ -47889,54 +47897,54 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D74">
-    <cfRule type="cellIs" dxfId="14" priority="27" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="14" priority="28" stopIfTrue="1" operator="between">
+      <formula>G74 * 0.7</formula>
+      <formula>G74 * 0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="29" stopIfTrue="1" operator="between">
+      <formula>G74 * 0.9</formula>
+      <formula>G74</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="27" stopIfTrue="1" operator="between">
       <formula>0</formula>
       <formula>G74 * 0.7</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="28" stopIfTrue="1" operator="between">
-      <formula>G74 * 0.7</formula>
-      <formula>G74 * 0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="29" stopIfTrue="1" operator="between">
-      <formula>G74 * 0.9</formula>
-      <formula>G74</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H23:H68">
-    <cfRule type="cellIs" dxfId="11" priority="1" stopIfTrue="1" operator="equal">
-      <formula>"na"</formula>
+    <cfRule type="cellIs" dxfId="11" priority="3" stopIfTrue="1" operator="equal">
+      <formula>G23-1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="10" priority="4" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>G23</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="2" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>G23-2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="3" stopIfTrue="1" operator="equal">
-      <formula>G23-1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>G23</formula>
+    <cfRule type="cellIs" dxfId="8" priority="1" stopIfTrue="1" operator="equal">
+      <formula>"na"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H78:H103">
-    <cfRule type="cellIs" dxfId="7" priority="9" stopIfTrue="1" operator="equal">
-      <formula>"na"</formula>
+    <cfRule type="cellIs" dxfId="7" priority="19" stopIfTrue="1" operator="greaterThanOrEqual">
+      <formula>G78</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="10" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="18" stopIfTrue="1" operator="equal">
+      <formula>G78-1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="17" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>G78-2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="11" stopIfTrue="1" operator="equal">
-      <formula>G78-1</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="4" priority="12" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>G78</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="17" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="11" stopIfTrue="1" operator="equal">
+      <formula>G78-1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="10" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>G78-2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" stopIfTrue="1" operator="equal">
-      <formula>G78-1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="19" stopIfTrue="1" operator="greaterThanOrEqual">
-      <formula>G78</formula>
+    <cfRule type="cellIs" dxfId="1" priority="9" stopIfTrue="1" operator="equal">
+      <formula>"na"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H78:J103">
@@ -47975,11 +47983,11 @@
   <sheetData>
     <row r="1" spans="1:43" ht="62.25" customHeight="1">
       <c r="A1" s="43"/>
-      <c r="B1" s="393" t="s">
+      <c r="B1" s="391" t="s">
         <v>1285</v>
       </c>
-      <c r="C1" s="394"/>
-      <c r="D1" s="394"/>
+      <c r="C1" s="392"/>
+      <c r="D1" s="392"/>
       <c r="E1" s="345"/>
       <c r="F1" s="346"/>
       <c r="G1" s="345"/>
@@ -48069,15 +48077,15 @@
       <c r="A3" s="49" t="s">
         <v>712</v>
       </c>
-      <c r="B3" s="395" t="s">
+      <c r="B3" s="393" t="s">
         <v>713</v>
       </c>
       <c r="C3" s="389"/>
-      <c r="D3" s="392" t="s">
+      <c r="D3" s="394" t="s">
         <v>714</v>
       </c>
-      <c r="E3" s="392"/>
-      <c r="F3" s="392"/>
+      <c r="E3" s="394"/>
+      <c r="F3" s="394"/>
       <c r="G3" s="389" t="s">
         <v>715</v>
       </c>
@@ -48086,23 +48094,23 @@
         <v>716</v>
       </c>
       <c r="J3" s="389"/>
-      <c r="K3" s="392" t="s">
+      <c r="K3" s="394" t="s">
         <v>717</v>
       </c>
-      <c r="L3" s="392"/>
+      <c r="L3" s="394"/>
       <c r="M3" s="389"/>
       <c r="N3" s="389" t="s">
         <v>718</v>
       </c>
       <c r="O3" s="389"/>
-      <c r="P3" s="396" t="s">
+      <c r="P3" s="395" t="s">
         <v>719</v>
       </c>
-      <c r="Q3" s="396"/>
-      <c r="R3" s="396" t="s">
+      <c r="Q3" s="395"/>
+      <c r="R3" s="395" t="s">
         <v>720</v>
       </c>
-      <c r="S3" s="396"/>
+      <c r="S3" s="395"/>
       <c r="T3" s="345"/>
       <c r="U3" s="389" t="s">
         <v>721</v>
@@ -48127,11 +48135,11 @@
       <c r="AE3" s="389"/>
       <c r="AF3" s="390"/>
       <c r="AG3" s="390"/>
-      <c r="AH3" s="391" t="s">
+      <c r="AH3" s="396" t="s">
         <v>726</v>
       </c>
-      <c r="AI3" s="391"/>
-      <c r="AJ3" s="392" t="s">
+      <c r="AI3" s="396"/>
+      <c r="AJ3" s="394" t="s">
         <v>727</v>
       </c>
       <c r="AK3" s="389"/>
@@ -49569,6 +49577,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="AD3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AP3:AQ3"/>
     <mergeCell ref="AA3:AC3"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B3:C3"/>
@@ -49582,11 +49595,6 @@
     <mergeCell ref="W3:X3"/>
     <mergeCell ref="Y3:Z3"/>
     <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AD3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AJ3:AK3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AP3:AQ3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId1"/>
@@ -49594,56 +49602,30 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ProcessingStatus xmlns="57d7cf67-1e42-43c7-8981-345bbe735d2d" xsi:nil="true"/>
-    <NewSpec xmlns="57d7cf67-1e42-43c7-8981-345bbe735d2d" xsi:nil="true"/>
-    <Done xmlns="57d7cf67-1e42-43c7-8981-345bbe735d2d" xsi:nil="true"/>
-    <TaxCatchAll xmlns="80829257-9d42-4cb3-95ef-c9211e8a54d3" xsi:nil="true"/>
-    <Comments xmlns="57d7cf67-1e42-43c7-8981-345bbe735d2d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="57d7cf67-1e42-43c7-8981-345bbe735d2d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Trafo_x002d_Done_x0028_Y_x002f_N_x0029_ xmlns="57d7cf67-1e42-43c7-8981-345bbe735d2d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001B6AF9AA6D4CC340A611240E5041F2F9" ma:contentTypeVersion="18" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="13e6f723ee29a5971814dec8f10b6dfd">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57d7cf67-1e42-43c7-8981-345bbe735d2d" xmlns:ns3="80829257-9d42-4cb3-95ef-c9211e8a54d3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f3302a8cf96e45e95ce30a55198ca1b5" ns2:_="" ns3:_="">
-    <xsd:import namespace="57d7cf67-1e42-43c7-8981-345bbe735d2d"/>
-    <xsd:import namespace="80829257-9d42-4cb3-95ef-c9211e8a54d3"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101008ACDBE60086FAA4F8F1D5A5D26C518DF" ma:contentTypeVersion="15" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="e83736769eb06572c99baa46e839d43c">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8d181bf8-2068-4739-8871-ee507501b2ce" xmlns:ns3="2d381071-7877-4367-bde3-715a0fe14163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="20b934b6093d6580b77eef392762e45a" ns2:_="" ns3:_="">
+    <xsd:import namespace="8d181bf8-2068-4739-8871-ee507501b2ce"/>
+    <xsd:import namespace="2d381071-7877-4367-bde3-715a0fe14163"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
+                <xsd:element ref="ns2:Description" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:Comments" minOccurs="0"/>
-                <xsd:element ref="ns2:ProcessingStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:NewSpec" minOccurs="0"/>
-                <xsd:element ref="ns2:Trafo_x002d_Done_x0028_Y_x002f_N_x0029_" minOccurs="0"/>
-                <xsd:element ref="ns2:Done" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:UpdateMaturity" minOccurs="0"/>
+                <xsd:element ref="ns2:Land_x002d_Standort_x002c_Entity_x002c_Werk_x002c_Warehouse" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -49651,105 +49633,98 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="57d7cf67-1e42-43c7-8981-345bbe735d2d" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8d181bf8-2068-4739-8871-ee507501b2ce" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+    <xsd:element name="Description" ma:index="8" nillable="true" ma:displayName="Description" ma:format="Dropdown" ma:internalName="Description">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="Comments" ma:index="11" nillable="true" ma:displayName="Comments" ma:format="Dropdown" ma:internalName="Comments">
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="UpdateMaturity" ma:index="16" nillable="true" ma:displayName="Update Maturity" ma:format="DateOnly" ma:internalName="UpdateMaturity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Land_x002d_Standort_x002c_Entity_x002c_Werk_x002c_Warehouse" ma:index="17" nillable="true" ma:displayName="Land-Standort, Entity, Werk, Warehouse" ma:description="Land, Standort, Entity, Werk, Warehouse" ma:format="Dropdown" ma:internalName="Land_x002d_Standort_x002c_Entity_x002c_Werk_x002c_Warehouse">
+      <xsd:simpleType>
+        <xsd:union memberTypes="dms:Text">
+          <xsd:simpleType>
+            <xsd:restriction base="dms:Choice">
+              <xsd:enumeration value="DE-L, Reutter-Group, HQ"/>
+              <xsd:enumeration value="DE-L, Reutter GmbH"/>
+              <xsd:enumeration value="AT-B, REUTTER GmbH"/>
+              <xsd:enumeration value="AT-G, REUTTER GmbH"/>
+              <xsd:enumeration value="SK-Myja, Reutter SK s.r.o., Plant"/>
+              <xsd:enumeration value="SK-Myja, Reutter SK s.r.o. Warehouse"/>
+              <xsd:enumeration value="PL-Mie,ITIB Poland SP. Z O.O., Plant"/>
+              <xsd:enumeration value="Overall Rating REUTIB"/>
+            </xsd:restriction>
+          </xsd:simpleType>
+        </xsd:union>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Bildmarkierungen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="43f40ce4-7bd6-448f-9c38-811a9ebee48e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="ProcessingStatus" ma:index="12" nillable="true" ma:displayName="Processing Status" ma:format="Dropdown" ma:internalName="ProcessingStatus">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="In Progress"/>
-          <xsd:enumeration value="In Review"/>
-          <xsd:enumeration value="Released for QBD.net"/>
-          <xsd:enumeration value="n/a"/>
-          <xsd:enumeration value="No Chg &amp;Adopted"/>
-          <xsd:enumeration value="Done - Takover KB"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="NewSpec" ma:index="13" nillable="true" ma:displayName="New Spec" ma:format="RadioButtons" ma:internalName="NewSpec">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="No"/>
-          <xsd:enumeration value="YES"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Trafo_x002d_Done_x0028_Y_x002f_N_x0029_" ma:index="14" nillable="true" ma:displayName="Trafo-Done (Y/N)" ma:description="Transformation of Policy/Standard/... done (Yes/No)" ma:format="Dropdown" ma:internalName="Trafo_x002d_Done_x0028_Y_x002f_N_x0029_">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="Yes"/>
-          <xsd:enumeration value="NO"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Done" ma:index="15" nillable="true" ma:displayName="Done" ma:format="Dropdown" ma:internalName="Done">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="Yes"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Bildmarkierungen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="43f40ce4-7bd6-448f-9c38-811a9ebee48e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="21" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="22" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="23" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="80829257-9d42-4cb3-95ef-c9211e8a54d3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2d381071-7877-4367-bde3-715a0fe14163" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{7eb975d3-f3be-4c06-8802-a37319f2eb99}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="80829257-9d42-4cb3-95ef-c9211e8a54d3">
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{fcfaaccf-5919-4008-9206-b09242b8c4bd}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="2d381071-7877-4367-bde3-715a0fe14163">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -49860,33 +49835,39 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8d181bf8-2068-4739-8871-ee507501b2ce">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Land_x002d_Standort_x002c_Entity_x002c_Werk_x002c_Warehouse xmlns="8d181bf8-2068-4739-8871-ee507501b2ce" xsi:nil="true"/>
+    <TaxCatchAll xmlns="2d381071-7877-4367-bde3-715a0fe14163" xsi:nil="true"/>
+    <UpdateMaturity xmlns="8d181bf8-2068-4739-8871-ee507501b2ce" xsi:nil="true"/>
+    <Description xmlns="8d181bf8-2068-4739-8871-ee507501b2ce" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC529B7A-DAAC-4760-A4B0-520EB2F8AA93}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="f169ebab-6c04-4927-8615-edf861aa3aa4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="fae5d43f-d09e-44b0-8410-ea430eb50bb2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB4B17D-A6E4-4120-B281-267F88333774}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4CC80C-90C7-46C7-A567-CC92C3206298}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47960F8D-54B8-4EC5-A083-3AD61AF115C6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B611CF4-3A10-44B0-ACBD-832685889F25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59D92808-F7DB-4EA0-8F5E-ABF35E9A85D4}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
